--- a/data/merged/2026-09-28/MERGED_IT_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_IT_Mite-Vacuum_2026-09-28.xlsx
@@ -4712,13 +4712,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4756,13 +4756,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4800,13 +4800,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5152,13 +5152,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5284,13 +5284,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5307,94 +5307,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId34" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Product 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId35" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Product 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId36" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5736,7 +5648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR37"/>
+  <dimension ref="A1:BR35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10162,52 +10074,52 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Marchio: ERINGOGO | Nome modello: Aspirapolvere per futon | Componenti inclusi: float balls | Peso articolo: 100 Grammi | Dimensioni vetrina articoli: 13,5 x 6,7 x 6,7 cm</t>
+          <t>Marchio: Liwankaqi | Caratteristica speciale: Stemless | Tipo di filtro: Panno | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ERINGOGO</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO Galleggiante per Lavasciuga Pavimenti Filtro per Serbatoio di Scarico Acciaio Inossidabile Parte Accessori Facile Installare Piccola Leggera</t>
+          <t>Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allergene per letto, divani, tappeti e molto altro ancora</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Filtro a Sfera Galleggiante Avanzato: Progettato per filtrare efficacemente le impurità nel serbatoio di scarico della lavapavimenti, garantendo una pulizia ottimale e proteggendo il system da ostruzioni
-Materiale in Acciaio Inossidabile Resistente: Realizzato con acciaio inossidabile, il filtro offre una lunga durata senza rischio di rottura o deformazione, mantenendo prestazioni costanti nel tempo
-Compatibilità Universale Con Lavapavimenti: Accessorio progettato per adattarsi a molteplici modelli di lavapavimenti, facilitando la sostituzione e la manutenzione del filtro nel serbatoio di scarico
-Installazione Facile E Veloce: Il filtro galleggiante può essere montato rapidamente senza attrezzi speciali, rendendo semplice la manutenzione ordinaria della lavapavimenti
-Design Compatto E Leggero: Dimensioni contenute (5,31*2,64*2,64in) e peso ridotto permettono un posizionamento pratico nel serbatoio senza influire sulla maneggevolezza della lavapavimenti</t>
+          <t>[Due potenti modalità di aspirazione per una perfetta igiene]: il nostro aspiracari per materassi offre due livelli di potenza, ideale per chi soffre di allergie. La potente aspirazione rimuove acari, polvere e pelle in modo affidabile. Perfetto come detergente per materassi per un ambiente igienico e pulito
+[Tecnologia UV e ad alta frequenza contro gli acari]: l'aspiracaro con UV combina 4 principi di azione: disinfezione UVC, ultrasuoni, rotazione della spazzola e potenza di aspirazione 8000 Pa. Il 99, 9% degli acari e dei batteri viene eliminato scientificamente
+[Innovativo sistema a 2 camere con capacità di 520 ml]: l'aspirapolvere antiacaro per materassi separa efficacemente allergeni e polvere grazie al filtro HEPA e ai contenitori trasparenti. Grande volume per meno vuoti, pratico per le famiglie
+[Leggero e intuitivo]: facile da usare grazie al design ergonomico dell'aspirapolvere manuale. I componenti possono essere rapidamente smontati e puliti. Particolarmente adatto per anziani e case allergiche
+[Utilizzo universale in tutta la casa]: non solo per materassi! Ideale per divani, tappeti, seggiolini auto e cucce per animali. Il potente tuttofare sostituisce costosi attrezzi speciali: il vostro pratico partner igienico per ogni stanza</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F8W81X7Y?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41y457dzzRL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0F8W81X7Y</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M21" s="14" t="inlineStr">
@@ -10221,7 +10133,7 @@
         </is>
       </c>
       <c r="O21" s="15">
-        <v>1867732</v>
+        <v>1070154</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="16">
@@ -10234,7 +10146,7 @@
       </c>
       <c r="S21" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T21" s="15"/>
@@ -10245,13 +10157,21 @@
       <c r="Y21" s="19">
         <v>1</v>
       </c>
-      <c r="Z21" s="20"/>
+      <c r="Z21" s="20">
+        <v>49.99</v>
+      </c>
       <c r="AA21" s="4"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="15"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="15"/>
-      <c r="AF21" s="21"/>
+      <c r="AD21" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE21" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="21">
+        <v>2.5</v>
+      </c>
       <c r="AG21" s="22">
         <v>0</v>
       </c>
@@ -10260,8 +10180,14 @@
         <v>0</v>
       </c>
       <c r="AJ21"/>
-      <c r="AK21" s="13"/>
-      <c r="AL21" s="19"/>
+      <c r="AK21" s="13" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AL21" s="19">
+        <v>409</v>
+      </c>
       <c r="AM21" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -10271,8 +10197,14 @@
       <c r="AO21" s="13"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="19"/>
-      <c r="AR21" s="19"/>
-      <c r="AS21" s="14"/>
+      <c r="AR21" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="14" t="inlineStr">
+        <is>
+          <t>liwantech</t>
+        </is>
+      </c>
       <c r="AT21" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -10280,14 +10212,26 @@
       </c>
       <c r="AU21" s="13"/>
       <c r="AV21" s="14"/>
-      <c r="AW21" s="13"/>
+      <c r="AW21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+        </is>
+      </c>
       <c r="AX21" s="13"/>
       <c r="AY21" s="13"/>
       <c r="AZ21" s="13"/>
       <c r="BA21" s="13"/>
       <c r="BB21" s="13"/>
-      <c r="BC21" s="13"/>
-      <c r="BD21" s="13"/>
+      <c r="BC21" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD21" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13"/>
       <c r="BG21" s="13"/>
@@ -10295,24 +10239,20 @@
       <c r="BI21" s="23"/>
       <c r="BJ21" s="23" t="inlineStr">
         <is>
-          <t>100 Grammi</t>
+          <t>2235 Grammi</t>
         </is>
       </c>
       <c r="BK21" s="23" t="inlineStr">
         <is>
-          <t>100.00 g</t>
+          <t>2.24 kg</t>
         </is>
       </c>
       <c r="BL21" s="23" t="inlineStr">
         <is>
-          <t>13,5 x 6,7 x 6,7 cm</t>
-        </is>
-      </c>
-      <c r="BM21" s="23" t="inlineStr">
-        <is>
-          <t>13.50 x 6.70 x 6.70 cm</t>
-        </is>
-      </c>
+          <t>29,5L x 2,7l x 18,5H cm</t>
+        </is>
+      </c>
+      <c r="BM21" s="23"/>
       <c r="BN21" s="23"/>
       <c r="BO21" s="23"/>
       <c r="BP21" s="23"/>
@@ -10326,52 +10266,56 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
-        </is>
-      </c>
-      <c r="D22" s="14"/>
+          <t>B0FBRWMG4G</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Colore: Bianco</t>
+        </is>
+      </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Liwankaqi | Caratteristica speciale: Stemless | Tipo di filtro: Panno | Superfici consigliate: Tutti i tipi di pavimento | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: Elecbee | Caratteristica speciale: Bassa rumorosità, Luce UV, Senza fili | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappeto, tappezz | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Elecbee</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.it/stores/Elecbee/page/523E80A7-9683-4D7C-910D-BDB5D37DE32D?lp_asin=B0FBRWMG4G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Aspiratore acaro per materassi, aspirapolvere acari con UVC e ultrasuoni, aspirazione 8KPa senza fili, anti-allergene per letto, divani, tappeti e molto altro ancora</t>
+          <t>Elecbee Battimaterasso Antiacaro, Pulisci Materasso Senza Filo, Aspirapolvere per Materassi, Sterilizzazione UV, Ideale per Materassi, Divani e Mobili Imbottiti, Ricarica di Tipo C</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>[Due potenti modalità di aspirazione per una perfetta igiene]: il nostro aspiracari per materassi offre due livelli di potenza, ideale per chi soffre di allergie. La potente aspirazione rimuove acari, polvere e pelle in modo affidabile. Perfetto come detergente per materassi per un ambiente igienico e pulito
-[Tecnologia UV e ad alta frequenza contro gli acari]: l'aspiracaro con UV combina 4 principi di azione: disinfezione UVC, ultrasuoni, rotazione della spazzola e potenza di aspirazione 8000 Pa. Il 99, 9% degli acari e dei batteri viene eliminato scientificamente
-[Innovativo sistema a 2 camere con capacità di 520 ml]: l'aspirapolvere antiacaro per materassi separa efficacemente allergeni e polvere grazie al filtro HEPA e ai contenitori trasparenti. Grande volume per meno vuoti, pratico per le famiglie
-[Leggero e intuitivo]: facile da usare grazie al design ergonomico dell'aspirapolvere manuale. I componenti possono essere rapidamente smontati e puliti. Particolarmente adatto per anziani e case allergiche
-[Utilizzo universale in tutta la casa]: non solo per materassi! Ideale per divani, tappeti, seggiolini auto e cucce per animali. Il potente tuttofare sostituisce costosi attrezzi speciali: il vostro pratico partner igienico per ogni stanza</t>
+          <t>【18.000 VIBRAZIONI PER MINUTE】 Il design a battito ad alta frequenza riproduce un movimento di picchiatura per aiutare a rimuovere polvere, peli e detriti presenti nelle fibre di materassi e tessuti. Una soluzione pratica per la manutenzione regolare della biancheria da letto.
+【Potente aspirazione di 13.000 Pa】 Grazie alla sua potenza di aspirazione di 13.000 Pa, questo aspirapolvere antiacaro aiuta a rimuovere polvere e sporco dopo il battito. È adatto per la pulizia quotidiana di materassi, divani e tappeti.
+【LUCE UV E TECNOLOGIA ULTRASONE】 Dotato di luce UV e tecnologia ad ultrasuoni, questo aspirapolvere per materasso combina due funzioni per la manutenzione delle superfici tessili. La luce UV e gli ultrasuoni vengono attivati in base alla modalità operativa selezionata.
+4 modalità di pulizia: le quattro funzioni Demite, ultrasuoni, spazzola a rullo e luce UV consentono di adattare la pulizia alle proprie esigenze. Il cambio di modalità viene effettuato utilizzando un pulsante, mentre il display a LED mostra chiaramente le informazioni operative.
+【SENZA FILI E RICARICA USB TYPE-C】Il design wireless facilita la pulizia di materassi, divani e tappeti senza essere limitato da una presa elettrica. La ricarica USB Type-C consente un comodo utilizzo a casa, in camera da letto o in altri spazi abitativi.</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FBRWMG4G?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Ol8d1f4bL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0H465J5XB</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
@@ -10385,7 +10329,7 @@
         </is>
       </c>
       <c r="O22" s="15">
-        <v>1070154</v>
+        <v>61651</v>
       </c>
       <c r="P22" s="15"/>
       <c r="Q22" s="16">
@@ -10398,7 +10342,7 @@
       </c>
       <c r="S22" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T22" s="15"/>
@@ -10407,22 +10351,22 @@
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
       <c r="Y22" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="20">
-        <v>49.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA22" s="4"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="15"/>
       <c r="AD22" s="19">
+        <v>23</v>
+      </c>
+      <c r="AE22" s="15">
         <v>2</v>
       </c>
-      <c r="AE22" s="15">
-        <v>0</v>
-      </c>
       <c r="AF22" s="21">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -10434,11 +10378,11 @@
       <c r="AJ22"/>
       <c r="AK22" s="13" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AL22" s="19">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="AM22" s="13" t="inlineStr">
         <is>
@@ -10454,7 +10398,7 @@
       </c>
       <c r="AS22" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
         </is>
       </c>
       <c r="AT22" s="13" t="inlineStr">
@@ -10466,7 +10410,7 @@
       <c r="AV22" s="14"/>
       <c r="AW22" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
         </is>
       </c>
       <c r="AX22" s="13"/>
@@ -10479,11 +10423,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD22" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD22" s="13"/>
       <c r="BE22" s="13"/>
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
@@ -10491,17 +10431,17 @@
       <c r="BI22" s="23"/>
       <c r="BJ22" s="23" t="inlineStr">
         <is>
-          <t>2235 Grammi</t>
+          <t>2000 Grammi</t>
         </is>
       </c>
       <c r="BK22" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>2.00 kg</t>
         </is>
       </c>
       <c r="BL22" s="23" t="inlineStr">
         <is>
-          <t>29,5L x 2,7l x 18,5H cm</t>
+          <t>30L x 32l x 21H cm</t>
         </is>
       </c>
       <c r="BM22" s="23"/>
@@ -10518,56 +10458,52 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FBRWMG4G</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Colore: Bianco</t>
-        </is>
-      </c>
+          <t>B0FKRC3KQY</t>
+        </is>
+      </c>
+      <c r="D23" s="14"/>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Elecbee | Caratteristica speciale: Bassa rumorosità, Luce UV, Senza fili | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappeto, tappezz | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: nan | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Elecbee</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Elecbee/page/523E80A7-9683-4D7C-910D-BDB5D37DE32D?lp_asin=B0FBRWMG4G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Battimaterasso Antiacaro, Pulisci Materasso Senza Filo, Aspirapolvere per Materassi, Sterilizzazione UV, Ideale per Materassi, Divani e Mobili Imbottiti, Ricarica di Tipo C</t>
+          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con contenitore per la polvere permanente, per materassi, divani, cuscini, tappeti</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>【18.000 VIBRAZIONI PER MINUTE】 Il design a battito ad alta frequenza riproduce un movimento di picchiatura per aiutare a rimuovere polvere, peli e detriti presenti nelle fibre di materassi e tessuti. Una soluzione pratica per la manutenzione regolare della biancheria da letto.
-【Potente aspirazione di 13.000 Pa】 Grazie alla sua potenza di aspirazione di 13.000 Pa, questo aspirapolvere antiacaro aiuta a rimuovere polvere e sporco dopo il battito. È adatto per la pulizia quotidiana di materassi, divani e tappeti.
-【LUCE UV E TECNOLOGIA ULTRASONE】 Dotato di luce UV e tecnologia ad ultrasuoni, questo aspirapolvere per materasso combina due funzioni per la manutenzione delle superfici tessili. La luce UV e gli ultrasuoni vengono attivati in base alla modalità operativa selezionata.
-4 modalità di pulizia: le quattro funzioni Demite, ultrasuoni, spazzola a rullo e luce UV consentono di adattare la pulizia alle proprie esigenze. Il cambio di modalità viene effettuato utilizzando un pulsante, mentre il display a LED mostra chiaramente le informazioni operative.
-【SENZA FILI E RICARICA USB TYPE-C】Il design wireless facilita la pulizia di materassi, divani e tappeti senza essere limitato da una presa elettrica. La ricarica USB Type-C consente un comodo utilizzo a casa, in camera da letto o in altri spazi abitativi.</t>
+          <t>【Leggero e compatto】 L'aspirapolvere da letto prende tre in una funzione di svolazzamento ad alta frequenza, forte aspirazione e penetrazione della luce viola. Doppio cuscinetto per pulsione, 253,7 nm, luce viola, più ampia area di pulizia, maggiore efficienza di pulizia.
+Design senza fili e leggero: goditi la libertà della pulizia wireless! La batteria ricaricabile offre una lunga durata di 30 minuti. Il nostro aspirapolvere è uno dei più leggeri sul mercato, il che lo rende più facile da usare e meno stress sui muscoli e sulle articolazioni. Il nostro design elegante e moderno si adatta alla tua estetica e all'arredamento della tua casa.
+Sistema di filtraggio ad alta efficienza: gli aspirapolvere per materassi utilizzano un filtro HEPA riutilizzabile e lavabile in combinazione con un tessuto filtrante in acciaio inox che può catturare circa il 99,97% delle particelle piccole come 0,3 micron, isolando le particelle di grandi dimensioni di spazzatura, bloccando saldamente polvere e sporco e non perderà.
+Scatola antipolvere lavabile: la macchina per la pulizia del materasso Snap-on, facile da pulire, può essere pulita direttamente sotto il rubinetto, pulizia regolare senza il fastidio della forza di aspirazione indebolita o della polvere intasata. Nota: il filtro deve essere utilizzato dopo l'asciugatura.
+Ambito di applicazione: l'aspirapolvere da letto può aspirare facilmente peli di animali domestici e peli di pelle, ecc. Adatto per superfici in tessuto: materassi, lenzuola, cuscini, tappeti, divani in tessuto, ecc. Il design antirumore non disturba il sonno di neonati o animali domestici.</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FBRWMG4G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Ol8d1f4bL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0H465J5XB</t>
+          <t>B0FKRC3KQY</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr">
@@ -10581,7 +10517,7 @@
         </is>
       </c>
       <c r="O23" s="15">
-        <v>61651</v>
+        <v>773814</v>
       </c>
       <c r="P23" s="15"/>
       <c r="Q23" s="16">
@@ -10594,7 +10530,7 @@
       </c>
       <c r="S23" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T23" s="15"/>
@@ -10603,22 +10539,22 @@
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="20">
-        <v>65.99</v>
+        <v>22.12</v>
       </c>
       <c r="AA23" s="4"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF23" s="21">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -10630,11 +10566,11 @@
       <c r="AJ23"/>
       <c r="AK23" s="13" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AL23" s="19">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="AM23" s="13" t="inlineStr">
         <is>
@@ -10650,7 +10586,7 @@
       </c>
       <c r="AS23" s="14" t="inlineStr">
         <is>
-          <t>WUHAN RENHOTEC TECHNOLOGY LTD</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT23" s="13" t="inlineStr">
@@ -10662,7 +10598,7 @@
       <c r="AV23" s="14"/>
       <c r="AW23" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX23" s="13"/>
@@ -10683,17 +10619,17 @@
       <c r="BI23" s="23"/>
       <c r="BJ23" s="23" t="inlineStr">
         <is>
-          <t>2000 Grammi</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="BK23" s="23" t="inlineStr">
         <is>
-          <t>2.00 kg</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL23" s="23" t="inlineStr">
         <is>
-          <t>30L x 32l x 21H cm</t>
+          <t>40L x 40l x 80H mm</t>
         </is>
       </c>
       <c r="BM23" s="23"/>
@@ -10710,48 +10646,48 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Marchio: JIGOO | Caratteristica speciale: Ipoallergenico | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappeto, Tappezzeria, Pavimento duro | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: Yaasier | Caratteristica speciale: Luce UV e HEPA | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria, materassi, tappeti | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspiratore Floreale Delight (Plant Essential Oil)</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 - Aspiratore antiacaro per materassi: Floral Delight (plant essential oil)</t>
+          <t>Luce UV e HEPA</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31va0mFb48L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FMRNV3RZ</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10765,7 +10701,7 @@
         </is>
       </c>
       <c r="O24" s="15">
-        <v>217003</v>
+        <v>519869</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="16">
@@ -10778,7 +10714,7 @@
       </c>
       <c r="S24" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T24" s="15"/>
@@ -10790,35 +10726,37 @@
         <v>1</v>
       </c>
       <c r="Z24" s="20">
-        <v>18.99</v>
+        <v>22.12</v>
       </c>
       <c r="AA24" s="4"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="15"/>
       <c r="AD24" s="19">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE24" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="21">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
       </c>
-      <c r="AH24" s="20"/>
+      <c r="AH24" s="20">
+        <v>5.12</v>
+      </c>
       <c r="AI24" s="16">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AJ24"/>
       <c r="AK24" s="13" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AL24" s="19">
-        <v>434</v>
+        <v>364</v>
       </c>
       <c r="AM24" s="13" t="inlineStr">
         <is>
@@ -10828,13 +10766,15 @@
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
       <c r="AP24" s="4"/>
-      <c r="AQ24" s="19"/>
+      <c r="AQ24" s="19">
+        <v>9</v>
+      </c>
       <c r="AR24" s="19">
         <v>1</v>
       </c>
       <c r="AS24" s="14" t="inlineStr">
         <is>
-          <t>yefengdianzi</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT24" s="13" t="inlineStr">
@@ -10842,11 +10782,19 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU24" s="13"/>
-      <c r="AV24" s="14"/>
+      <c r="AU24" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV24" s="14" t="inlineStr">
+        <is>
+          <t>dong hu xin ji shu hubei 430223 CN</t>
+        </is>
+      </c>
       <c r="AW24" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX24" s="13"/>
@@ -10854,38 +10802,58 @@
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13"/>
+      <c r="BC24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
-      <c r="BF24" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF24" s="13"/>
       <c r="BG24" s="13"/>
       <c r="BH24" s="14"/>
       <c r="BI24" s="23"/>
       <c r="BJ24" s="23" t="inlineStr">
         <is>
-          <t>50 g</t>
+          <t>400 grammi</t>
         </is>
       </c>
       <c r="BK24" s="23" t="inlineStr">
         <is>
-          <t>50.00 g</t>
+          <t>400.00 g</t>
         </is>
       </c>
       <c r="BL24" s="23" t="inlineStr">
         <is>
-          <t>6L x 1,3l x 8H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM24" s="23"/>
-      <c r="BN24" s="23"/>
-      <c r="BO24" s="23"/>
-      <c r="BP24" s="23"/>
-      <c r="BQ24" s="23"/>
-      <c r="BR24" s="13"/>
+      <c r="BN24" s="23" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="BO24" s="23" t="inlineStr">
+        <is>
+          <t>400.00 g</t>
+        </is>
+      </c>
+      <c r="BP24" s="23" t="inlineStr">
+        <is>
+          <t>23.4 x 11.9 x 10 cm</t>
+        </is>
+      </c>
+      <c r="BQ24" s="23" t="inlineStr">
+        <is>
+          <t>23.40 x 11.90 x 10.00 cm</t>
+        </is>
+      </c>
+      <c r="BR24" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
@@ -10894,52 +10862,52 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: nan | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: Teant | Caratteristica speciale: HEPA | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappeto | Fonte di alimentazione: Con cavo elettrico</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per acari con luce UV, mini aspirapolvere con filtro HEPA, Aspirapolvere portatile senza fili con contenitore per la polvere permanente, per materassi, divani, cuscini, tappeti</t>
+          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Display LED, Filtro HEPA, Calore a 65°C e Aromatizzante per Letto</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>【Leggero e compatto】 L'aspirapolvere da letto prende tre in una funzione di svolazzamento ad alta frequenza, forte aspirazione e penetrazione della luce viola. Doppio cuscinetto per pulsione, 253,7 nm, luce viola, più ampia area di pulizia, maggiore efficienza di pulizia.
-Design senza fili e leggero: goditi la libertà della pulizia wireless! La batteria ricaricabile offre una lunga durata di 30 minuti. Il nostro aspirapolvere è uno dei più leggeri sul mercato, il che lo rende più facile da usare e meno stress sui muscoli e sulle articolazioni. Il nostro design elegante e moderno si adatta alla tua estetica e all'arredamento della tua casa.
-Sistema di filtraggio ad alta efficienza: gli aspirapolvere per materassi utilizzano un filtro HEPA riutilizzabile e lavabile in combinazione con un tessuto filtrante in acciaio inox che può catturare circa il 99,97% delle particelle piccole come 0,3 micron, isolando le particelle di grandi dimensioni di spazzatura, bloccando saldamente polvere e sporco e non perderà.
-Scatola antipolvere lavabile: la macchina per la pulizia del materasso Snap-on, facile da pulire, può essere pulita direttamente sotto il rubinetto, pulizia regolare senza il fastidio della forza di aspirazione indebolita o della polvere intasata. Nota: il filtro deve essere utilizzato dopo l'asciugatura.
-Ambito di applicazione: l'aspirapolvere da letto può aspirare facilmente peli di animali domestici e peli di pelle, ecc. Adatto per superfici in tessuto: materassi, lenzuola, cuscini, tappeti, divani in tessuto, ecc. Il design antirumore non disturba il sonno di neonati o animali domestici.</t>
+          <t>Potente pulizia profonda a 2 livelli – lo sporco non sopravvive: l'aspiracari Teant offre 2 livelli di aspirazione regolabili fino a 18 kPa. Mentre il motore Hyper-Helix da 33.000 giri/min fornisce potenti movimenti di battitura per penetrare in materassi, divani e tessuti e sollevare polvere, pelle e allergeni. La doppia coppa antipolvere e un filtro HEPA catturano il 99,97% delle microparticelle (minimo fino a 0,3 µm) e separano i peli per evitare intasamenti. Ciò mantiene la forza di aspirazione per una pulizia più profonda e uniforme e una camera da letto più fresca
+[Rilevamento luce verde, nessuna polvere si nasconde] L'aspirapolvere per materassi Teant utilizza una luce verde da 555 nm e la tecnologia delle lenti per rendere visibili polvere nascosta, peli di animali e microparticelle su materassi scuri, divani e fessure di tessuto profonde, in modo da non tralasciare i punti. Il cavo extra lungo da 5 metri raggiunge ogni angolo di un materasso king size senza dover spostare. Sperimenta una pulizia più semplice, intelligente e accurata
+[Mira a microparticelle nascoste per proteggere la tua famiglia] 253,7 nm UV-C luce da acari Vacuum Cleaner combinato con tecnologia ad ultrasuoni 40.000 Hz. Teant aspiracari con luce UV penetra in profondità nelle fibre del materasso per combattere le particelle invisibili ed eliminare il 99,9%. I doppi rulli sensibili alla gravità attivano i raggi UV solo quando entrambe le ruote toccano la superficie per 2 secondi e si spengono quando viene sollevata. Può prevenire perdite di luce e mantenere al sicuro le vostre famiglie e animali domestici
+[Per una casa più fresca: calore, aroma &amp; anione] Dì goodbye a letti e odori umidi! L'aspirapolvere per materassi Teant fornisce un flusso d'aria riscaldato a 65 °C per asciugare i tessuti in modo efficiente: goditi un materasso pulito e asciutto. La tecnologia agli ioni negativi aiuta a neutralizzare le particelle sospese nell'aria e a rinfrescare l'aria. La compressa aromatica rimuove gli odori e aggiunge un sottile profumo naturale, perfetto per una notte di sonno pulito e accogliente
+[Doppia protezione: spazzola anti-groviglio e protezione contro il surriscaldamento] Teant aspiracari con luce UV dispone di una spazzola a rullo con arresto automatico che si ferma immediatamente quando si aggroviglia, proteggendo il motore e prolungando la durata. La protezione da surriscaldamento integrata interrompe automaticamente il funzionamento dopo un uso prolungato. Basta spegnere, lasciare raffreddare per 2 ore e continuare a pulire con fiducia</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FKRC3KQY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41B+I610d+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FKRC3KQY</t>
+          <t>B0FN3GPQZM</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
@@ -10953,7 +10921,7 @@
         </is>
       </c>
       <c r="O25" s="15">
-        <v>773814</v>
+        <v>962620</v>
       </c>
       <c r="P25" s="15"/>
       <c r="Q25" s="16">
@@ -10966,7 +10934,7 @@
       </c>
       <c r="S25" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T25" s="15"/>
@@ -10978,19 +10946,19 @@
         <v>1</v>
       </c>
       <c r="Z25" s="20">
-        <v>22.12</v>
+        <v>131.98</v>
       </c>
       <c r="AA25" s="4"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="19">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF25" s="21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -11002,11 +10970,11 @@
       <c r="AJ25"/>
       <c r="AK25" s="13" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AL25" s="19">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="AM25" s="13" t="inlineStr">
         <is>
@@ -11022,7 +10990,7 @@
       </c>
       <c r="AS25" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="AT25" s="13" t="inlineStr">
@@ -11034,7 +11002,7 @@
       <c r="AV25" s="14"/>
       <c r="AW25" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
         </is>
       </c>
       <c r="AX25" s="13"/>
@@ -11049,23 +11017,23 @@
       </c>
       <c r="BD25" s="13"/>
       <c r="BE25" s="13"/>
-      <c r="BF25" s="13"/>
+      <c r="BF25" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG25" s="13"/>
       <c r="BH25" s="14"/>
       <c r="BI25" s="23"/>
       <c r="BJ25" s="23" t="inlineStr">
         <is>
-          <t>400 g</t>
-        </is>
-      </c>
-      <c r="BK25" s="23" t="inlineStr">
-        <is>
-          <t>400.00 g</t>
-        </is>
-      </c>
+          <t>1,9 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK25" s="23"/>
       <c r="BL25" s="23" t="inlineStr">
         <is>
-          <t>40L x 40l x 80H mm</t>
+          <t>23L x 27l x 25H cm</t>
         </is>
       </c>
       <c r="BM25" s="23"/>
@@ -11082,48 +11050,52 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Yaasier | Caratteristica speciale: Luce UV e HEPA | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria, materassi, tappeti | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: PattenlLevi | Caratteristica speciale: Lampade UV ad alta frequenza, 3 modalità di pulizia, Protezione di sicurezza | Superfici consigliate: Per l'interno dell'auto | Fonte di alimentazione: A batteria | Componenti inclusi: Cavo USB, Manuale di istruzioni in inglese</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>PattenlLevi</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
+          <t>Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per letti, materassi, cuscini</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>Luce UV e HEPA</t>
+          <t>Libera molte diverse superfici tessili dal 99% di acari e allergeni.
+Nota: per garantire la funzione automatica di pianificazione del percorso della macchina di rimozione degli acari del divano durante l'uso, si prega di rimuovere gli ostacoli vicini, i piccoli oggetti non possono essere bloccati accanto alla macchina.
+3 modalità di pulizia: dispone della modalità manuale con la copertura chiusa, la modalità automatica premendo una volta e la modalità di gattonamento del letto premendo due volte.
+Protezione di sicurezza: una volta sollevato il dispositivo, la lampada UV si spegne automaticamente per evitare che la luce ultravioletta diretta danneggi gli occhi e la pelle. È dotato di 3 set di sensori a infrarossi e 2 set di sensori di collisione a infrarossi, che possono impedire fino a un certo grado di impedire che cada dal letto e rilevare i limiti del materasso, degli ostacoli, ecc.
+Risparmio energetico intelligente: in modalità automatica, il consumo energetico è di soli 3,5 W, in modalità manuale scende a 3 W, che è sia efficiente dal punto di vista energetico che rispettoso dell'ambiente. Dispone di una batteria al litio ad alta capacità (2000 mAh) che offre una lunga durata e può essere utilizzata ininterrotta per circa 120 minuti con una carica completa.</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FMRNV3RZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/215WpAtX06L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FMRNV3RZ</t>
+          <t>B0FP52HNHM</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -11137,7 +11109,7 @@
         </is>
       </c>
       <c r="O26" s="15">
-        <v>519869</v>
+        <v>1705694</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="16">
@@ -11150,7 +11122,7 @@
       </c>
       <c r="S26" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T26" s="15"/>
@@ -11161,39 +11133,27 @@
       <c r="Y26" s="19">
         <v>1</v>
       </c>
-      <c r="Z26" s="20">
-        <v>22.12</v>
-      </c>
+      <c r="Z26" s="20"/>
       <c r="AA26" s="4"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="15"/>
       <c r="AD26" s="19">
-        <v>13</v>
-      </c>
-      <c r="AE26" s="15">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE26" s="15"/>
       <c r="AF26" s="21">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
-      <c r="AH26" s="20">
-        <v>5.12</v>
-      </c>
+      <c r="AH26" s="20"/>
       <c r="AI26" s="16">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AJ26"/>
-      <c r="AK26" s="13" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AL26" s="19">
-        <v>364</v>
-      </c>
+      <c r="AK26" s="13"/>
+      <c r="AL26" s="19"/>
       <c r="AM26" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -11202,94 +11162,42 @@
       <c r="AN26" s="13"/>
       <c r="AO26" s="13"/>
       <c r="AP26" s="4"/>
-      <c r="AQ26" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR26" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS26" s="14" t="inlineStr">
-        <is>
-          <t>Renyu</t>
-        </is>
-      </c>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="14"/>
       <c r="AT26" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU26" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV26" s="14" t="inlineStr">
-        <is>
-          <t>dong hu xin ji shu hubei 430223 CN</t>
-        </is>
-      </c>
-      <c r="AW26" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
-        </is>
-      </c>
+      <c r="AU26" s="13"/>
+      <c r="AV26" s="14"/>
+      <c r="AW26" s="13"/>
       <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
       <c r="AZ26" s="13"/>
       <c r="BA26" s="13"/>
       <c r="BB26" s="13"/>
-      <c r="BC26" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC26" s="13"/>
       <c r="BD26" s="13"/>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
       <c r="BH26" s="14"/>
       <c r="BI26" s="23"/>
-      <c r="BJ26" s="23" t="inlineStr">
-        <is>
-          <t>400 grammi</t>
-        </is>
-      </c>
-      <c r="BK26" s="23" t="inlineStr">
-        <is>
-          <t>400.00 g</t>
-        </is>
-      </c>
+      <c r="BJ26" s="23"/>
+      <c r="BK26" s="23"/>
       <c r="BL26" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H cm</t>
+          <t>16L x 16l x 5H cm</t>
         </is>
       </c>
       <c r="BM26" s="23"/>
-      <c r="BN26" s="23" t="inlineStr">
-        <is>
-          <t>400 g</t>
-        </is>
-      </c>
-      <c r="BO26" s="23" t="inlineStr">
-        <is>
-          <t>400.00 g</t>
-        </is>
-      </c>
-      <c r="BP26" s="23" t="inlineStr">
-        <is>
-          <t>23.4 x 11.9 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BQ26" s="23" t="inlineStr">
-        <is>
-          <t>23.40 x 11.90 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BR26" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+      <c r="BN26" s="23"/>
+      <c r="BO26" s="23"/>
+      <c r="BP26" s="23"/>
+      <c r="BQ26" s="23"/>
+      <c r="BR26" s="13"/>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
@@ -11298,52 +11206,53 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0FP9CGZYN</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Teant | Caratteristica speciale: HEPA | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappeto | Fonte di alimentazione: Con cavo elettrico</t>
+          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Teant Aspirapolvere per Materassi, 2 Velocità (14 kPa/18 kPa) – con Rilevamento Polvere a Luce Verde, Luce UV-C 253.7 nm, Display LED, Filtro HEPA, Calore a 65°C e Aromatizzante per Letto</t>
+          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento Rapido, Aspirapolvere antiacari per materassi, letti,divani</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>Potente pulizia profonda a 2 livelli – lo sporco non sopravvive: l'aspiracari Teant offre 2 livelli di aspirazione regolabili fino a 18 kPa. Mentre il motore Hyper-Helix da 33.000 giri/min fornisce potenti movimenti di battitura per penetrare in materassi, divani e tessuti e sollevare polvere, pelle e allergeni. La doppia coppa antipolvere e un filtro HEPA catturano il 99,97% delle microparticelle (minimo fino a 0,3 µm) e separano i peli per evitare intasamenti. Ciò mantiene la forza di aspirazione per una pulizia più profonda e uniforme e una camera da letto più fresca
-[Rilevamento luce verde, nessuna polvere si nasconde] L'aspirapolvere per materassi Teant utilizza una luce verde da 555 nm e la tecnologia delle lenti per rendere visibili polvere nascosta, peli di animali e microparticelle su materassi scuri, divani e fessure di tessuto profonde, in modo da non tralasciare i punti. Il cavo extra lungo da 5 metri raggiunge ogni angolo di un materasso king size senza dover spostare. Sperimenta una pulizia più semplice, intelligente e accurata
-[Mira a microparticelle nascoste per proteggere la tua famiglia] 253,7 nm UV-C luce da acari Vacuum Cleaner combinato con tecnologia ad ultrasuoni 40.000 Hz. Teant aspiracari con luce UV penetra in profondità nelle fibre del materasso per combattere le particelle invisibili ed eliminare il 99,9%. I doppi rulli sensibili alla gravità attivano i raggi UV solo quando entrambe le ruote toccano la superficie per 2 secondi e si spengono quando viene sollevata. Può prevenire perdite di luce e mantenere al sicuro le vostre famiglie e animali domestici
-[Per una casa più fresca: calore, aroma &amp; anione] Dì goodbye a letti e odori umidi! L'aspirapolvere per materassi Teant fornisce un flusso d'aria riscaldato a 65 °C per asciugare i tessuti in modo efficiente: goditi un materasso pulito e asciutto. La tecnologia agli ioni negativi aiuta a neutralizzare le particelle sospese nell'aria e a rinfrescare l'aria. La compressa aromatica rimuove gli odori e aggiunge un sottile profumo naturale, perfetto per una notte di sonno pulito e accogliente
-[Doppia protezione: spazzola anti-groviglio e protezione contro il surriscaldamento] Teant aspiracari con luce UV dispone di una spazzola a rullo con arresto automatico che si ferma immediatamente quando si aggroviglia, proteggendo il motore e prolungando la durata. La protezione da surriscaldamento integrata interrompe automaticamente il funzionamento dopo un uso prolungato. Basta spegnere, lasciare raffreddare per 2 ore e continuare a pulire con fiducia</t>
+          <t>【Potente pulizia profonda con forte aspirazione e rullo ad alta velocità】 Questo aspirapolvere per materassi combina una forte aspirazione di 13.000 Pa con una spazzola a rullo ad alta velocità di 30.000 giri/min per rimuovere efficacemente polvere, particelle e detriti incrostati in profondità nei materassi, nei divani e nei cuscini, garantendo un'agitazione potente e una pulizia profonda e accurata con il minimo sforzo.
+【Design multifunzionale】 Questo aspiratore antiacaro per materassi è dotato di luce UV-C a 253,7 nm, rilevamento intelligente della polvere, tecnologia a ultrasuoni e rotazione della spazzola ad alta frequenza, che aiutano a rimuovere le particelle di polvere fine incrostata in profondità.
+【Design a doppio contenitore per la polvere e sistema di filtraggio multistrato】 Il doppio contenitore per la polvere da 520 ml può contenere più polvere e detriti, separando efficacemente la polvere e i rifiuti per un'esperienza più pulita e igienica. Questo strumento di pulizia è dotato di un sistema di filtraggio multistrato, che include un filtro HEPA e uno strato di spugna, in grado di assorbire efficacemente le particelle di polvere fine per garantire un ambiente pulito
+【Design leggero e senza fili】: Pulsante di avvio one-touch, due modalità di aspirazione. Questo aspirapolvere è dotato di una batteria ricaricabile e può funzionare fino a 35 minuti in modalità a bassa velocità e fino a 20 minuti in modalità ad alta velocità. Il design senza fili rende inoltre l'aspirapolvere per divani più flessibile e comodo, più facile da spostare.
+【Potente aspirazione da 16Kpa】 Questo aspirapolvere per biancheria da letto ha una potenza di aspirazione super da 16Kpa, in grado di aspirare efficacemente polvere, lanugine fine e altri detriti da varie superfici come letti, culle, materassi, divani, tappeti, ecc., garantendo ogni volta una pulizia profonda e accurata. Non utilizzare su superfici dure (come scrivanie, pavimenti)
+【Regali di compleanno unici】: Questo potente aspiratore acari per materassi è contenuto in una confezione colorata dal design accattivante, che lo rende un regalo pratico e premuroso per la mamma e il papà. Include anche un filtro HEPA di ricambio, un cavo di ricarica e un manuale d'uso.</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FN3GPQZM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41B+I610d+L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41FJHPfdNGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FN3GPQZM</t>
+          <t>B0C5372Y5G</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -11357,7 +11266,7 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>962620</v>
+        <v>751540</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="16">
@@ -11370,7 +11279,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -11382,19 +11291,19 @@
         <v>1</v>
       </c>
       <c r="Z27" s="20">
-        <v>131.98</v>
+        <v>78.99</v>
       </c>
       <c r="AA27" s="4"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="15"/>
       <c r="AD27" s="19">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AE27" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -11406,11 +11315,11 @@
       <c r="AJ27"/>
       <c r="AK27" s="13" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AL27" s="19">
-        <v>383</v>
+        <v>636</v>
       </c>
       <c r="AM27" s="13" t="inlineStr">
         <is>
@@ -11426,7 +11335,7 @@
       </c>
       <c r="AS27" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Renyu</t>
         </is>
       </c>
       <c r="AT27" s="13" t="inlineStr">
@@ -11438,7 +11347,7 @@
       <c r="AV27" s="14"/>
       <c r="AW27" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
         </is>
       </c>
       <c r="AX27" s="13"/>
@@ -11451,25 +11360,29 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD27" s="13"/>
+      <c r="BD27" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE27" s="13"/>
-      <c r="BF27" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF27" s="13"/>
       <c r="BG27" s="13"/>
       <c r="BH27" s="14"/>
       <c r="BI27" s="23"/>
       <c r="BJ27" s="23" t="inlineStr">
         <is>
-          <t>1,9 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK27" s="23"/>
+          <t>250 Grammi</t>
+        </is>
+      </c>
+      <c r="BK27" s="23" t="inlineStr">
+        <is>
+          <t>250.00 g</t>
+        </is>
+      </c>
       <c r="BL27" s="23" t="inlineStr">
         <is>
-          <t>23L x 27l x 25H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM27" s="23"/>
@@ -11486,52 +11399,53 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Marchio: PattenlLevi | Caratteristica speciale: Lampade UV ad alta frequenza, 3 modalità di pulizia, Protezione di sicurezza | Superfici consigliate: Per l'interno dell'auto | Fonte di alimentazione: A batteria | Componenti inclusi: Cavo USB, Manuale di istruzioni in inglese</t>
+          <t>Marchio: MITE GUARD | Caratteristica speciale: Luce UV | Tipo di filtro: Filtro HEPA | Superfici consigliate: Materassi, tappezzeria, divani, tappeti | Fonte di alimentazione: Con cavo elettrico</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi</t>
+          <t>MITE GUARD</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Aspiratore per materassi da 3 a 3,5 W, 3 modalità di pulizia Robot sterilizzazione automatico con luce UV per letti, materassi, cuscini</t>
+          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a 60 °C, detergente per materassi, tettarella contro acari della polvere</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>Libera molte diverse superfici tessili dal 99% di acari e allergeni.
-Nota: per garantire la funzione automatica di pianificazione del percorso della macchina di rimozione degli acari del divano durante l'uso, si prega di rimuovere gli ostacoli vicini, i piccoli oggetti non possono essere bloccati accanto alla macchina.
-3 modalità di pulizia: dispone della modalità manuale con la copertura chiusa, la modalità automatica premendo una volta e la modalità di gattonamento del letto premendo due volte.
-Protezione di sicurezza: una volta sollevato il dispositivo, la lampada UV si spegne automaticamente per evitare che la luce ultravioletta diretta danneggi gli occhi e la pelle. È dotato di 3 set di sensori a infrarossi e 2 set di sensori di collisione a infrarossi, che possono impedire fino a un certo grado di impedire che cada dal letto e rilevare i limiti del materasso, degli ostacoli, ecc.
-Risparmio energetico intelligente: in modalità automatica, il consumo energetico è di soli 3,5 W, in modalità manuale scende a 3 W, che è sia efficiente dal punto di vista energetico che rispettoso dell'ambiente. Dispone di una batteria al litio ad alta capacità (2000 mAh) che offre una lunga durata e può essere utilizzata ininterrotta per circa 120 minuti con una carica completa.</t>
+          <t>Nuovo su Amazon! Migliore sonno senza sintomi allergici. Libera materassi, divani e tappeti da acari, batteri e peli di animali. Luce UV, funzione di riscaldamento a 60 °C e ultrasuoni che riducono sensibilmente gli allergeni per un sonno riposante. Dormi come un re con l'aspirapolvere MiteGuard.
+Doppio potere pulente: esclusivo con accessori speciali per peli di animali e superfici delicate. Morbido con i tessuti, resistente agli acari e alla polvere, ideale per case con allergie.
+Pulizia profonda facile: potenza di aspirazione super forte da 16 kPa combinata con sistema di filtro HEPA con filtro HEPA e filtro di ricambio. Sicuro per tutta la famiglia, igienico e a bassa manutenzione.
+Massima flessibilità: grazie al suo cavo da 6 m, questo aspirapolvere antiacaro offre un ampio raggio d'azione per una pulizia comoda in tutta la casa e perfetto per famiglie con bambini e proprietari di animali domestici.
+Per una pulizia profonda: l'aspirapolvere per acari con luce UV funziona direttamente sulla fontana. Il detergente per materassi scioglie i residui in profondità nei tessuti e gli ultrasuoni contro gli acari interferiscono con lo sviluppo sostenibile.
+MiteGuard, il tuo marchio tedesco per un sonno riposante. Affidatevi alla qualità testata e al supporto esperto. Lo sapevi già? Gli ultrasuoni interferiscono con la moltiplicazione degli acari per una freschezza e un benessere duraturi</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP52HNHM?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/215WpAtX06L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51Q5Ecf20kL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FP52HNHM</t>
+          <t>B0FRBB876G</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -11545,7 +11459,7 @@
         </is>
       </c>
       <c r="O28" s="15">
-        <v>1705694</v>
+        <v>1626167</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="16">
@@ -11558,7 +11472,7 @@
       </c>
       <c r="S28" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T28" s="15"/>
@@ -11574,11 +11488,11 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="15"/>
       <c r="AD28" s="19">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -11617,15 +11531,23 @@
       <c r="BC28" s="13"/>
       <c r="BD28" s="13"/>
       <c r="BE28" s="13"/>
-      <c r="BF28" s="13"/>
+      <c r="BF28" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG28" s="13"/>
       <c r="BH28" s="14"/>
       <c r="BI28" s="23"/>
-      <c r="BJ28" s="23"/>
+      <c r="BJ28" s="23" t="inlineStr">
+        <is>
+          <t>2,2 Chilogrammi</t>
+        </is>
+      </c>
       <c r="BK28" s="23"/>
       <c r="BL28" s="23" t="inlineStr">
         <is>
-          <t>16L x 16l x 5H cm</t>
+          <t>28L x 22l x 25H cm</t>
         </is>
       </c>
       <c r="BM28" s="23"/>
@@ -11642,53 +11564,53 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FP9CGZYN</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: JIGOO | Caratteristica speciale: Luce UV | Tipo di filtro: Schiuma | Superfici consigliate: Tappezzeria | Fonte di alimentazione: Con cavo elettrico</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere per materassi,16kpa Battimaterasso Antiacaro con luce UV-C a 253,7nm, Rimuove il 99,9%, Riscaldamento Rapido, Aspirapolvere antiacari per materassi, letti,divani</t>
+          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa oltre il 95% dei requisiti.</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>【Potente pulizia profonda con forte aspirazione e rullo ad alta velocità】 Questo aspirapolvere per materassi combina una forte aspirazione di 13.000 Pa con una spazzola a rullo ad alta velocità di 30.000 giri/min per rimuovere efficacemente polvere, particelle e detriti incrostati in profondità nei materassi, nei divani e nei cuscini, garantendo un'agitazione potente e una pulizia profonda e accurata con il minimo sforzo.
-【Design multifunzionale】 Questo aspiratore antiacaro per materassi è dotato di luce UV-C a 253,7 nm, rilevamento intelligente della polvere, tecnologia a ultrasuoni e rotazione della spazzola ad alta frequenza, che aiutano a rimuovere le particelle di polvere fine incrostata in profondità.
-【Design a doppio contenitore per la polvere e sistema di filtraggio multistrato】 Il doppio contenitore per la polvere da 520 ml può contenere più polvere e detriti, separando efficacemente la polvere e i rifiuti per un'esperienza più pulita e igienica. Questo strumento di pulizia è dotato di un sistema di filtraggio multistrato, che include un filtro HEPA e uno strato di spugna, in grado di assorbire efficacemente le particelle di polvere fine per garantire un ambiente pulito
-【Design leggero e senza fili】: Pulsante di avvio one-touch, due modalità di aspirazione. Questo aspirapolvere è dotato di una batteria ricaricabile e può funzionare fino a 35 minuti in modalità a bassa velocità e fino a 20 minuti in modalità ad alta velocità. Il design senza fili rende inoltre l'aspirapolvere per divani più flessibile e comodo, più facile da spostare.
-【Potente aspirazione da 16Kpa】 Questo aspirapolvere per biancheria da letto ha una potenza di aspirazione super da 16Kpa, in grado di aspirare efficacemente polvere, lanugine fine e altri detriti da varie superfici come letti, culle, materassi, divani, tappeti, ecc., garantendo ogni volta una pulizia profonda e accurata. Non utilizzare su superfici dure (come scrivanie, pavimenti)
-【Regali di compleanno unici】: Questo potente aspiratore acari per materassi è contenuto in una confezione colorata dal design accattivante, che lo rende un regalo pratico e premuroso per la mamma e il papà. Include anche un filtro HEPA di ricambio, un cavo di ricarica e un manuale d'uso.</t>
+          <t>Pulizia ad alte prestazioni: l'aspirapolvere per materassi JIGOO T600 rende la pulizia un gioco da ragazzi. Dotato di due potenti motori digitali brushless, raggiunge una vera potenza di 700 W e genera una potenza di aspirazione di 15 kPa. L'apertura di aspirazione larga 23,5 cm controlla facilmente la pulizia di grandi letti e divani lunghi.
+Risultato di pulizia perfetto: l'aspirapolvere per materassi elimina facilmente batteri e acari grazie alla luce UV con una lunghezza d'onda di 253,7 nm, che uccide le cellule degli acari. Successivamente, gli acari vengono disturbati dagli ultrasuoni e limitati nella loro vitalità. Un flusso d'aria calda di 60 °C asciuga il materasso, rimuove gli acari dalla base della vita e crea un ambiente pulito e sano in modo permanente.
+Filtraggio degli acari al 99,9% e purificazione dell'aria: l'innovativo sistema a contenitore chiuso impedisce il ritorno della polvere ed evita l'inquinamento secondario dell'aria, così gli acari della polvere vengono filtrati al 99,9% e rilasciano aria pura. Quando viene utilizzato un modulo di profumo, l'aspirapolvere emette ioni negativi profumati durante il funzionamento che puliscono ulteriormente l'aria e donano alla stanza una piacevole freschezza.
+Display LED: un display a LED chiaro mostra in qualsiasi momento lo stato di funzionamento del dispositivo. Il sensore intelligente integrato rileva con precisione gli acari sul materasso, mentre il display mostra i progressi di pulizia in tempo reale. La combinazione di sensore e display aumenta la precisione e l'efficienza del processo di pulizia. Ulteriori luci funzionali indicano chiaramente lo stato di funzionamento.
+Design intelligente: la forma ergonomica si adatta bene alla mano e rende l'uso particolarmente confortevole. Le ruote nella parte inferiore garantiscono uno spostamento senza sforzo. Una particolare caratteristica di sicurezza protegge gli occhi: la lampada UVC si attiva solo quando entrambe le ruote vengono premute verso il basso. Un semplice funzionamento con un pulsante e componenti facilmente smontabili facilitano la pulizia e la manutenzione.
+Servizio e vicinanza al cliente: il prodotto può invecchiare con il tempo, ma la nostra cura rimane costante. Dal momento in cui scegliete noi, non siamo solo il vostro rivenditore, ma anche un partner affidabile. Se hai bisogno di noi, siamo qui per te, con una semplice risposta alla tua domanda, con un supporto dedicato. Il nostro obiettivo è quello di stare al tuo fianco e accompagnarti a lungo termine.</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FP9CGZYN?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41FJHPfdNGL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41TzkiwaXvL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0C5372Y5G</t>
+          <t>B0FW3MWVJR</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -11702,7 +11624,7 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>751540</v>
+        <v>571192</v>
       </c>
       <c r="P29" s="15"/>
       <c r="Q29" s="16">
@@ -11715,7 +11637,7 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T29" s="15"/>
@@ -11727,19 +11649,19 @@
         <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>78.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA29" s="4"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="15"/>
       <c r="AD29" s="19">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="AE29" s="15">
         <v>0</v>
       </c>
       <c r="AF29" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -11751,11 +11673,11 @@
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>636</v>
+        <v>328</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -11771,7 +11693,7 @@
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Renyu</t>
+          <t>ANISE EDALS52</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
@@ -11783,7 +11705,7 @@
       <c r="AV29" s="14"/>
       <c r="AW29" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
         </is>
       </c>
       <c r="AX29" s="13"/>
@@ -11791,16 +11713,8 @@
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD29" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC29" s="13"/>
+      <c r="BD29" s="13"/>
       <c r="BE29" s="13"/>
       <c r="BF29" s="13"/>
       <c r="BG29" s="13"/>
@@ -11808,17 +11722,17 @@
       <c r="BI29" s="23"/>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>250 Grammi</t>
+          <t>2,72 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>250.00 g</t>
+          <t>2.72 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H cm</t>
+          <t>27,2L x 18,8l x 32,9H cm</t>
         </is>
       </c>
       <c r="BM29" s="23"/>
@@ -11835,53 +11749,52 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Marchio: MITE GUARD | Caratteristica speciale: Luce UV | Tipo di filtro: Filtro HEPA | Superfici consigliate: Materassi, tappezzeria, divani, tappeti | Fonte di alimentazione: Con cavo elettrico</t>
+          <t>Marchio: Yaasier | Caratteristica speciale: Tecnologia avanzata tre in uno: cuscinetto di pulsazione a doppio battito e luce UV da 253,7 nm | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria , Pavimenti | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>MITE GUARD</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Miteguard Aspiratore per materassi e imbottiture con 2 spazzole speciali – Luce UV, dispositivo ad ultrasuoni &amp; aria calda a 60 °C, detergente per materassi, tettarella contro acari della polvere</t>
+          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>Nuovo su Amazon! Migliore sonno senza sintomi allergici. Libera materassi, divani e tappeti da acari, batteri e peli di animali. Luce UV, funzione di riscaldamento a 60 °C e ultrasuoni che riducono sensibilmente gli allergeni per un sonno riposante. Dormi come un re con l'aspirapolvere MiteGuard.
-Doppio potere pulente: esclusivo con accessori speciali per peli di animali e superfici delicate. Morbido con i tessuti, resistente agli acari e alla polvere, ideale per case con allergie.
-Pulizia profonda facile: potenza di aspirazione super forte da 16 kPa combinata con sistema di filtro HEPA con filtro HEPA e filtro di ricambio. Sicuro per tutta la famiglia, igienico e a bassa manutenzione.
-Massima flessibilità: grazie al suo cavo da 6 m, questo aspirapolvere antiacaro offre un ampio raggio d'azione per una pulizia comoda in tutta la casa e perfetto per famiglie con bambini e proprietari di animali domestici.
-Per una pulizia profonda: l'aspirapolvere per acari con luce UV funziona direttamente sulla fontana. Il detergente per materassi scioglie i residui in profondità nei tessuti e gli ultrasuoni contro gli acari interferiscono con lo sviluppo sostenibile.
-MiteGuard, il tuo marchio tedesco per un sonno riposante. Affidatevi alla qualità testata e al supporto esperto. Lo sapevi già? Gli ultrasuoni interferiscono con la moltiplicazione degli acari per una freschezza e un benessere duraturi</t>
+          <t>Tecnologia avanzata tre in uno: dotato di un pad di pulsazione a doppio battito e luce UV da 253,7 nm, questo aspirapolvere offre una grande area di pulizia e una maggiore efficienza, ideale per rimuovere acari della polvere e altri allergeni dai materassi e dai tessuti. Con un cuscinetto a pulsazione a doppio battito e luce UV da 253,7 nm, questo aspirapolvere offre una grande area di pulizia e una maggiore efficienza. zum Entfernen von Hausstaubacari e altri allergeni dai vostri materassi e tessuti.
+Design senza fili leggero: massimizza la tua comodità con questo leggero aspirapolvere senza fili, dotato di una batteria ricaricabile che offre una durata fino a 30 minuti. Il suo design moderno ed elegante si adatta perfettamente a qualsiasi arredamento e rende la pulizia senza sforzo.
+Sistema di filtraggio ad alta efficienza: il pulitore per materassi con un filtro HEPA lavabile e un filtro in cotone sull'uscita, questo aspirapolvere cattura il 99,97% delle particelle di polvere fine, garantisce aria più sana e riduce l'inquinamento secondario, ideale per persone sensibili e famiglie con bambini.
+Contenitore della polvere lavabile facile da pulire: l'aspirapolvere con il contenitore della polvere lavabile sotto l'acqua corrente rende più facile pulire il vostro aspirapolvere. Asciugare il filtro prima del riutilizzo per garantire prestazioni di aspirazione ottimali e prestazioni di pulizia costanti.
+Versatilità e comfort d'uso: aspirapolvere antiacaro con luce UV, ideale per aspirare peli di animali e forfora su diverse superfici in tessuto come materassi, cuscini, divani e tappeti. Goditi una pulizia silenziosa che non disturba neonati o animali domestici che dormono</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FRBB876G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51Q5Ecf20kL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FRBB876G</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -11895,7 +11808,7 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>1626167</v>
+        <v>1226272</v>
       </c>
       <c r="P30" s="15"/>
       <c r="Q30" s="16">
@@ -11908,7 +11821,7 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T30" s="15"/>
@@ -11924,11 +11837,11 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="15"/>
       <c r="AD30" s="19">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="AE30" s="15"/>
       <c r="AF30" s="21">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -11964,26 +11877,26 @@
       <c r="AZ30" s="13"/>
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
-      <c r="BC30" s="13"/>
-      <c r="BD30" s="13"/>
+      <c r="BC30" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD30" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE30" s="13"/>
-      <c r="BF30" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF30" s="13"/>
       <c r="BG30" s="13"/>
       <c r="BH30" s="14"/>
       <c r="BI30" s="23"/>
-      <c r="BJ30" s="23" t="inlineStr">
-        <is>
-          <t>2,2 Chilogrammi</t>
-        </is>
-      </c>
+      <c r="BJ30" s="23"/>
       <c r="BK30" s="23"/>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>28L x 22l x 25H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM30" s="23"/>
@@ -12000,53 +11913,52 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0GJS592V3</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Marchio: JIGOO | Caratteristica speciale: Luce UV | Tipo di filtro: Schiuma | Superfici consigliate: Tappezzeria | Fonte di alimentazione: Con cavo elettrico</t>
+          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tessuto | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>JIGOO</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Battimaterasso, Aspiratore per acari Soluzione economica, completamente funzionale, con tutti gli accessori. Soddisfa oltre il 95% dei requisiti.</t>
+          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>Pulizia ad alte prestazioni: l'aspirapolvere per materassi JIGOO T600 rende la pulizia un gioco da ragazzi. Dotato di due potenti motori digitali brushless, raggiunge una vera potenza di 700 W e genera una potenza di aspirazione di 15 kPa. L'apertura di aspirazione larga 23,5 cm controlla facilmente la pulizia di grandi letti e divani lunghi.
-Risultato di pulizia perfetto: l'aspirapolvere per materassi elimina facilmente batteri e acari grazie alla luce UV con una lunghezza d'onda di 253,7 nm, che uccide le cellule degli acari. Successivamente, gli acari vengono disturbati dagli ultrasuoni e limitati nella loro vitalità. Un flusso d'aria calda di 60 °C asciuga il materasso, rimuove gli acari dalla base della vita e crea un ambiente pulito e sano in modo permanente.
-Filtraggio degli acari al 99,9% e purificazione dell'aria: l'innovativo sistema a contenitore chiuso impedisce il ritorno della polvere ed evita l'inquinamento secondario dell'aria, così gli acari della polvere vengono filtrati al 99,9% e rilasciano aria pura. Quando viene utilizzato un modulo di profumo, l'aspirapolvere emette ioni negativi profumati durante il funzionamento che puliscono ulteriormente l'aria e donano alla stanza una piacevole freschezza.
-Display LED: un display a LED chiaro mostra in qualsiasi momento lo stato di funzionamento del dispositivo. Il sensore intelligente integrato rileva con precisione gli acari sul materasso, mentre il display mostra i progressi di pulizia in tempo reale. La combinazione di sensore e display aumenta la precisione e l'efficienza del processo di pulizia. Ulteriori luci funzionali indicano chiaramente lo stato di funzionamento.
-Design intelligente: la forma ergonomica si adatta bene alla mano e rende l'uso particolarmente confortevole. Le ruote nella parte inferiore garantiscono uno spostamento senza sforzo. Una particolare caratteristica di sicurezza protegge gli occhi: la lampada UVC si attiva solo quando entrambe le ruote vengono premute verso il basso. Un semplice funzionamento con un pulsante e componenti facilmente smontabili facilitano la pulizia e la manutenzione.
-Servizio e vicinanza al cliente: il prodotto può invecchiare con il tempo, ma la nostra cura rimane costante. Dal momento in cui scegliete noi, non siamo solo il vostro rivenditore, ma anche un partner affidabile. Se hai bisogno di noi, siamo qui per te, con una semplice risposta alla tua domanda, con un supporto dedicato. Il nostro obiettivo è quello di stare al tuo fianco e accompagnarti a lungo termine.</t>
+          <t>【Leggero e compatto】 L'aspirapolvere da letto prende tre in una funzione di svolazzamento ad alta frequenza, forte aspirazione e penetrazione della luce viola. Doppio cuscinetto per pulsione, 253,7 nm, luce viola, più ampia area di pulizia, maggiore efficienza di pulizia
+【Design senza fili e leggero】Goditi la libertà della pulizia wireless! La batteria ricaricabile offre una lunga durata di 30 minuti. Il nostro aspiracaro per materassi è uno dei più leggeri sul mercato, rendendolo più facile da usare e meno stress sui muscoli e sulle articolazioni. Il nostro design elegante e moderno si adatta alla tua estetica e all'arredamento della tua casa
+【Sistema di filtraggio ad alta efficienza】 Gli aspirapolvere per materassi utilizzano un filtro HEPA riutilizzabile e lavabile e profondamente pulito in combinazione con un tessuto filtrante in acciaio inox che può catturare circa il 99,97% delle particelle piccole come 0,3 micron, isolando le particelle di grandi dimensioni di spazzatura, bloccano saldamente polvere e sporco e non fuoriesce
+【Scatola antipolvere lavabile】Aspiracari senza fili, scatola per la polvere Snap-on, facile da pulire, può essere pulita direttamente sotto il rubinetto, pulizia regolare senza il fastidio della forza di aspirazione indebolita o della polvere intasata. Nota: il filtro deve essere utilizzato dopo l'asciugatura
+【Ambito di applicazione】 la batteria per aspiracari può facilmente assorbire peli di animali e peli di animali domestici, ecc. Adatto per superfici in tessuto: materassi, lenzuola, cuscini, tappeti, divani in tessuto, ecc. Il design antirumore non disturba il sonno di neonati o animali domestici</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FW3MWVJR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41TzkiwaXvL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31vsJlUl+mL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FW3MWVJR</t>
+          <t>B0HG52FLCZ</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -12060,7 +11972,7 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>571192</v>
+        <v>536201</v>
       </c>
       <c r="P31" s="15"/>
       <c r="Q31" s="16">
@@ -12073,7 +11985,7 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T31" s="15"/>
@@ -12084,20 +11996,16 @@
       <c r="Y31" s="19">
         <v>1</v>
       </c>
-      <c r="Z31" s="20">
-        <v>65.99</v>
-      </c>
+      <c r="Z31" s="20"/>
       <c r="AA31" s="4"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="15"/>
       <c r="AD31" s="19">
-        <v>3</v>
-      </c>
-      <c r="AE31" s="15">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="AE31" s="15"/>
       <c r="AF31" s="21">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -12107,14 +12015,8 @@
         <v>0</v>
       </c>
       <c r="AJ31"/>
-      <c r="AK31" s="13" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AL31" s="19">
-        <v>328</v>
-      </c>
+      <c r="AK31" s="13"/>
+      <c r="AL31" s="19"/>
       <c r="AM31" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12124,14 +12026,8 @@
       <c r="AO31" s="13"/>
       <c r="AP31" s="4"/>
       <c r="AQ31" s="19"/>
-      <c r="AR31" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS31" s="14" t="inlineStr">
-        <is>
-          <t>ANISE EDALS52</t>
-        </is>
-      </c>
+      <c r="AR31" s="19"/>
+      <c r="AS31" s="14"/>
       <c r="AT31" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12139,17 +12035,17 @@
       </c>
       <c r="AU31" s="13"/>
       <c r="AV31" s="14"/>
-      <c r="AW31" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6</t>
-        </is>
-      </c>
+      <c r="AW31" s="13"/>
       <c r="AX31" s="13"/>
       <c r="AY31" s="13"/>
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
-      <c r="BC31" s="13"/>
+      <c r="BC31" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD31" s="13"/>
       <c r="BE31" s="13"/>
       <c r="BF31" s="13"/>
@@ -12158,17 +12054,17 @@
       <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>2,72 kg</t>
+          <t>250 Grammi</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>2.72 kg</t>
+          <t>250.00 g</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>27,2L x 18,8l x 32,9H cm</t>
+          <t>6L x 4l x 8H cm</t>
         </is>
       </c>
       <c r="BM31" s="23"/>
@@ -12185,52 +12081,56 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
-        </is>
-      </c>
-      <c r="D32" s="14"/>
+          <t>B0GT17NK5X</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Colore: Lilla</t>
+        </is>
+      </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Yaasier | Caratteristica speciale: Tecnologia avanzata tre in uno: cuscinetto di pulsazione a doppio battito e luce UV da 253,7 nm | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tappezzeria , Pavimenti | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: XINYUDAILY | Caratteristica speciale: Luce UV | Superfici consigliate: Tappezzeria | È cordless?: Sì | Capacità: 520 ml</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/XINYUDAILY/b/ref=bl_dp_s_web_85008070031?ie=UTF8&amp;node=85008070031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
+          <t>Aspirapolvere per acari senza fili per materassi, con luce UV da 253,7 nm, ultrasuoni e battitura con rullo a spazzola, per rimuovere acari della polvere, allergeni e peli di animali (viola)</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>Tecnologia avanzata tre in uno: dotato di un pad di pulsazione a doppio battito e luce UV da 253,7 nm, questo aspirapolvere offre una grande area di pulizia e una maggiore efficienza, ideale per rimuovere acari della polvere e altri allergeni dai materassi e dai tessuti. Con un cuscinetto a pulsazione a doppio battito e luce UV da 253,7 nm, questo aspirapolvere offre una grande area di pulizia e una maggiore efficienza. zum Entfernen von Hausstaubacari e altri allergeni dai vostri materassi e tessuti.
-Design senza fili leggero: massimizza la tua comodità con questo leggero aspirapolvere senza fili, dotato di una batteria ricaricabile che offre una durata fino a 30 minuti. Il suo design moderno ed elegante si adatta perfettamente a qualsiasi arredamento e rende la pulizia senza sforzo.
-Sistema di filtraggio ad alta efficienza: il pulitore per materassi con un filtro HEPA lavabile e un filtro in cotone sull'uscita, questo aspirapolvere cattura il 99,97% delle particelle di polvere fine, garantisce aria più sana e riduce l'inquinamento secondario, ideale per persone sensibili e famiglie con bambini.
-Contenitore della polvere lavabile facile da pulire: l'aspirapolvere con il contenitore della polvere lavabile sotto l'acqua corrente rende più facile pulire il vostro aspirapolvere. Asciugare il filtro prima del riutilizzo per garantire prestazioni di aspirazione ottimali e prestazioni di pulizia costanti.
-Versatilità e comfort d'uso: aspirapolvere antiacaro con luce UV, ideale per aspirare peli di animali e forfora su diverse superfici in tessuto come materassi, cuscini, divani e tappeti. Goditi una pulizia silenziosa che non disturba neonati o animali domestici che dormono</t>
+          <t>Efficiente pulizia profonda 4 in 1: il nostro pulitore per materassi senza fili combina 4 tecnologie avanzate: potente aspirazione da 13 kPa, un rullo a spazzola con 18.000 colpi/min, luce UV-C da 253,7 nm per sterilizzazione e ultrasuoni. Rimuove facilmente lo sporco incrostato, gli acari della polvere, gli allergeni e i batteri da materassi, biancheria da letto, divani e imbottiture. Crea un ambiente di sonno più pulito e sano per la tua famiglia.
+Doppio contenitore e sistema di filtraggio multilivello: il design sofisticato con due contenitori separati per la polvere (520 ml) separa efficacemente polvere e rifiuti dall'aria, il che non solo è più igienico, ma garantisce anche una potenza di aspirazione costantemente elevata. In combinazione con il sistema di filtraggio multistrato, il 99,99% delle particelle più sottili vengono trattenute in modo affidabile, ideale per chi soffre di allergie.
+VISUALIZZAZIONE LED &amp; LIBERTÀ SENZA FILI: Quattro modalità di pulizia (aspirazione/ultrasuoni/rullo spazzola/luce UV-C) possono essere comodamente commutate con un pulsante, con una visualizzazione chiara sul display LED. Il design leggero e senza fili offre la massima libertà di movimento. La potente batteria offre fino a 35 minuti di autonomia in modalità Eco e 20 minuti in modalità Boost – sufficiente per la pulizia accurata di camera da letto e soggiorno.
+Leggero, compatto e versatile: grazie al peso ridotto e alla forma compatta, questo aspirapolvere a mano è perfettamente maneggevole. Pulisce non solo materassi e divani, ma anche tappeti, cuscini, sedili auto e altri tessuti senza sforzo.
+REGALO PREMUROSO: Questo pulitore per materassi non è solo un pratico elettrodomestico, ma anche un'idea regalo ideale per i tuoi cari, confezionato in una bella confezione regalo.</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51XxVKRglXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0GXBZHWFJ</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -12244,7 +12144,7 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>1226272</v>
+        <v>98439</v>
       </c>
       <c r="P32" s="15"/>
       <c r="Q32" s="16">
@@ -12257,7 +12157,7 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T32" s="15"/>
@@ -12268,16 +12168,20 @@
       <c r="Y32" s="19">
         <v>1</v>
       </c>
-      <c r="Z32" s="20"/>
+      <c r="Z32" s="20">
+        <v>69.99</v>
+      </c>
       <c r="AA32" s="4"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="15"/>
       <c r="AD32" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="AE32" s="15">
+        <v>0</v>
+      </c>
       <c r="AF32" s="21">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -12287,8 +12191,14 @@
         <v>0</v>
       </c>
       <c r="AJ32"/>
-      <c r="AK32" s="13"/>
-      <c r="AL32" s="19"/>
+      <c r="AK32" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AL32" s="19">
+        <v>155</v>
+      </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12298,8 +12208,14 @@
       <c r="AO32" s="13"/>
       <c r="AP32" s="4"/>
       <c r="AQ32" s="19"/>
-      <c r="AR32" s="19"/>
-      <c r="AS32" s="14"/>
+      <c r="AR32" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="14" t="inlineStr">
+        <is>
+          <t>XINYU-EU</t>
+        </is>
+      </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12307,17 +12223,17 @@
       </c>
       <c r="AU32" s="13"/>
       <c r="AV32" s="14"/>
-      <c r="AW32" s="13"/>
+      <c r="AW32" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+        </is>
+      </c>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13"/>
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
-      <c r="BC32" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC32" s="13"/>
       <c r="BD32" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12328,11 +12244,19 @@
       <c r="BG32" s="13"/>
       <c r="BH32" s="14"/>
       <c r="BI32" s="23"/>
-      <c r="BJ32" s="23"/>
-      <c r="BK32" s="23"/>
+      <c r="BJ32" s="23" t="inlineStr">
+        <is>
+          <t>2,2 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK32" s="23" t="inlineStr">
+        <is>
+          <t>2.20 kg</t>
+        </is>
+      </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H cm</t>
+          <t>32L x 29l x 21H cm</t>
         </is>
       </c>
       <c r="BM32" s="23"/>
@@ -12349,52 +12273,52 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GJS592V3</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Yaasier | Caratteristica speciale: Portatile | Tipo di filtro: Filtro HEPA | Superfici consigliate: Tessuto | Fonte di alimentazione: A batteria</t>
+          <t>Marchio: Vehiwell | Caratteristica speciale: Luce UV | È cordless?: No | Capacità: 500 ml | Fattore di forma: Portatile</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Yaasier</t>
+          <t>Vehiwell</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirapolvere antiacaro per acari, Battimaterasso antiacaro con luce UV e contenitore per polvere permanente HEPA, Aspiratore Anticari per divano/materasso/tessile</t>
+          <t>Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>【Leggero e compatto】 L'aspirapolvere da letto prende tre in una funzione di svolazzamento ad alta frequenza, forte aspirazione e penetrazione della luce viola. Doppio cuscinetto per pulsione, 253,7 nm, luce viola, più ampia area di pulizia, maggiore efficienza di pulizia
-【Design senza fili e leggero】Goditi la libertà della pulizia wireless! La batteria ricaricabile offre una lunga durata di 30 minuti. Il nostro aspiracaro per materassi è uno dei più leggeri sul mercato, rendendolo più facile da usare e meno stress sui muscoli e sulle articolazioni. Il nostro design elegante e moderno si adatta alla tua estetica e all'arredamento della tua casa
-【Sistema di filtraggio ad alta efficienza】 Gli aspirapolvere per materassi utilizzano un filtro HEPA riutilizzabile e lavabile e profondamente pulito in combinazione con un tessuto filtrante in acciaio inox che può catturare circa il 99,97% delle particelle piccole come 0,3 micron, isolando le particelle di grandi dimensioni di spazzatura, bloccano saldamente polvere e sporco e non fuoriesce
-【Scatola antipolvere lavabile】Aspiracari senza fili, scatola per la polvere Snap-on, facile da pulire, può essere pulita direttamente sotto il rubinetto, pulizia regolare senza il fastidio della forza di aspirazione indebolita o della polvere intasata. Nota: il filtro deve essere utilizzato dopo l'asciugatura
-【Ambito di applicazione】 la batteria per aspiracari può facilmente assorbire peli di animali e peli di animali domestici, ecc. Adatto per superfici in tessuto: materassi, lenzuola, cuscini, tappeti, divani in tessuto, ecc. Il design antirumore non disturba il sonno di neonati o animali domestici</t>
+          <t>Forte aspirazione: questo aspirapolvere antiacaro è dotato di un motore da 600 W con una potenza di aspirazione massima di 15 kPa. La potenza di aspirazione è regolabile in due livelli e rimuove efficacemente acari e polvere.
+Luce UV-C: questo aspiratore antiacaro è dotato di una lampada UV-C con sensore intelligente. Si spegne automaticamente non appena il dispositivo viene rimosso dalla superficie. In questo modo si evitano alte temperature e garantiscono una rimozione sicura degli acari senza irritazioni della pelle.
+Separazione della polvere e degli acari: il contenitore della polvere presenta un design a doppio contenitore con una capacità totale di 500 ml. Il contenitore sinistro serve per il filtraggio, mentre il contenitore destro raccoglie polvere e acari.
+Tripla filtrazione: questo aspiratore antiacaro include un filtro fine in acciaio inossidabile che trattiene le particelle grossolane, ovatta filtrante ad alta densità che filtra particelle fino a 0,3 micron e un contenitore trasparente per catturare particelle visibili e più grandi.
+Riutilizzabile: il contenitore della polvere è rimovibile, si smonta facilmente con un solo pulsante e può essere riutilizzato dopo la pulizia.</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJS592V3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31vsJlUl+mL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41+tCP4liDL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0HG52FLCZ</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -12408,7 +12332,7 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>536201</v>
+        <v>1441388</v>
       </c>
       <c r="P33" s="15"/>
       <c r="Q33" s="16">
@@ -12421,7 +12345,7 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T33" s="15"/>
@@ -12436,13 +12360,9 @@
       <c r="AA33" s="4"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="15"/>
-      <c r="AD33" s="19">
-        <v>28</v>
-      </c>
+      <c r="AD33" s="19"/>
       <c r="AE33" s="15"/>
-      <c r="AF33" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AF33" s="21"/>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
@@ -12488,19 +12408,11 @@
       <c r="BG33" s="13"/>
       <c r="BH33" s="14"/>
       <c r="BI33" s="23"/>
-      <c r="BJ33" s="23" t="inlineStr">
-        <is>
-          <t>250 Grammi</t>
-        </is>
-      </c>
-      <c r="BK33" s="23" t="inlineStr">
-        <is>
-          <t>250.00 g</t>
-        </is>
-      </c>
+      <c r="BJ33" s="23"/>
+      <c r="BK33" s="23"/>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>6L x 4l x 8H cm</t>
+          <t>34L x 28l x 22H cm</t>
         </is>
       </c>
       <c r="BM33" s="23"/>
@@ -12517,56 +12429,52 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Colore: Lilla</t>
-        </is>
-      </c>
+          <t>B0H418FY5Y</t>
+        </is>
+      </c>
+      <c r="D34" s="14"/>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Marchio: XINYUDAILY | Caratteristica speciale: Luce UV | Superfici consigliate: Tappezzeria | È cordless?: Sì | Capacità: 520 ml</t>
+          <t>Marchio: Lubluelu | Caratteristica speciale: Luce UV | Superfici consigliate: Tappezzeria | Fonte di alimentazione: Con cavo elettrico | È cordless?: No</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>XINYUDAILY</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/XINYUDAILY/b/ref=bl_dp_s_web_85008070031?ie=UTF8&amp;node=85008070031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
+          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere per acari senza fili per materassi, con luce UV da 253,7 nm, ultrasuoni e battitura con rullo a spazzola, per rimuovere acari della polvere, allergeni e peli di animali (viola)</t>
+          <t>Lubluelu Pulitore per materassi 3 in 1 con potenza di aspirazione da 20 kPa, aspirapolvere antiacaro con funzione battitore e funzione di calore, aspirapolvere manuale per materassi, divani e</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>Efficiente pulizia profonda 4 in 1: il nostro pulitore per materassi senza fili combina 4 tecnologie avanzate: potente aspirazione da 13 kPa, un rullo a spazzola con 18.000 colpi/min, luce UV-C da 253,7 nm per sterilizzazione e ultrasuoni. Rimuove facilmente lo sporco incrostato, gli acari della polvere, gli allergeni e i batteri da materassi, biancheria da letto, divani e imbottiture. Crea un ambiente di sonno più pulito e sano per la tua famiglia.
-Doppio contenitore e sistema di filtraggio multilivello: il design sofisticato con due contenitori separati per la polvere (520 ml) separa efficacemente polvere e rifiuti dall'aria, il che non solo è più igienico, ma garantisce anche una potenza di aspirazione costantemente elevata. In combinazione con il sistema di filtraggio multistrato, il 99,99% delle particelle più sottili vengono trattenute in modo affidabile, ideale per chi soffre di allergie.
-VISUALIZZAZIONE LED &amp; LIBERTÀ SENZA FILI: Quattro modalità di pulizia (aspirazione/ultrasuoni/rullo spazzola/luce UV-C) possono essere comodamente commutate con un pulsante, con una visualizzazione chiara sul display LED. Il design leggero e senza fili offre la massima libertà di movimento. La potente batteria offre fino a 35 minuti di autonomia in modalità Eco e 20 minuti in modalità Boost – sufficiente per la pulizia accurata di camera da letto e soggiorno.
-Leggero, compatto e versatile: grazie al peso ridotto e alla forma compatta, questo aspirapolvere a mano è perfettamente maneggevole. Pulisce non solo materassi e divani, ma anche tappeti, cuscini, sedili auto e altri tessuti senza sforzo.
-REGALO PREMUROSO: Questo pulitore per materassi non è solo un pratico elettrodomestico, ma anche un'idea regalo ideale per i tuoi cari, confezionato in una bella confezione regalo.</t>
+          <t>Tecnologia di pulizia 3 in 1 per tessuti igienici: la combinazione di spazzola rotante, funzione battitore e supporto termico aiuta a rimuovere polvere, acari e allergeni dalle superfici del tessuto e a migliorare la pulizia di materassi e mobili imbottiti.
+Potente aspirazione da 20 kPa per una pulizia profonda: con una forte potenza di aspirazione di 20.000 Pa, l'aspirapolvere acari rimuove in modo affidabile polvere, sporco e particelle sottili da materassi, divani, piumini, tappeti e altre superfici tessili.
+Versatile su varie superfici in tessuto: ideale per materassi, tappezzeria, lenzuola, coperte, tappeti e peluche. Perfettamente adatto per la pulizia regolare di camera da letto, soggiorno e cameretta dei bambini.
+Pulizia senza additivi chimici: la combinazione di movimento meccanico e funzione termica supporta una pulizia efficace senza detergenti aggiuntivi. Particolarmente adatto per case con bambini, animali domestici o persone allergiche.
+Design compatto per una comoda maneggevolezza: il leggero dispositivo portatile dispone di un cavo di alimentazione da 4 metri per una maggiore libertà di movimento. Il contenitore della polvere è facile da svuotare e il sistema di filtraggio è facile da pulire per l'uso quotidiano.</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H418FY5Y?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51XxVKRglXL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GXBZHWFJ</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -12580,7 +12488,7 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>98439</v>
+        <v>228781</v>
       </c>
       <c r="P34" s="15"/>
       <c r="Q34" s="16">
@@ -12593,7 +12501,7 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T34" s="15"/>
@@ -12605,19 +12513,19 @@
         <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>69.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA34" s="4"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AE34" s="15">
         <v>0</v>
       </c>
       <c r="AF34" s="21">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -12629,11 +12537,11 @@
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
@@ -12649,7 +12557,7 @@
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Lubluelu Official</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -12661,7 +12569,7 @@
       <c r="AV34" s="14"/>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
@@ -12670,29 +12578,29 @@
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
       <c r="BC34" s="13"/>
-      <c r="BD34" s="13" t="inlineStr">
+      <c r="BD34" s="13"/>
+      <c r="BE34" s="13"/>
+      <c r="BF34" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE34" s="13"/>
-      <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
       <c r="BH34" s="14"/>
       <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>2,2 Kilograms</t>
+          <t>2,34 Kilograms</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>2.34 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>32L x 29l x 21H cm</t>
+          <t>42L x 31l x 18H cm</t>
         </is>
       </c>
       <c r="BM34" s="23"/>
@@ -12709,52 +12617,57 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
-        </is>
-      </c>
-      <c r="D35" s="14"/>
+          <t>B0HFN6BP5R</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Colore: Bianco Crema + Argento</t>
+        </is>
+      </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>Marchio: Vehiwell | Caratteristica speciale: Luce UV | È cordless?: No | Capacità: 500 ml | Fattore di forma: Portatile</t>
+          <t>Marchio: Lubluelu | Caratteristica speciale: Luce UV | Tipo di filtro: Filtro in acciaio inox e spugna | Superfici consigliate: Materassi, divani, tappeti, biancheria da letto, imbottiti, tessuti | Fonte di alimentazione: A batteria</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell</t>
+          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0HFN6BP5R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Aspirapolvere per acari, 15 kPa, detergente per materassi con luce UV-C</t>
+          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-C</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>Forte aspirazione: questo aspirapolvere antiacaro è dotato di un motore da 600 W con una potenza di aspirazione massima di 15 kPa. La potenza di aspirazione è regolabile in due livelli e rimuove efficacemente acari e polvere.
-Luce UV-C: questo aspiratore antiacaro è dotato di una lampada UV-C con sensore intelligente. Si spegne automaticamente non appena il dispositivo viene rimosso dalla superficie. In questo modo si evitano alte temperature e garantiscono una rimozione sicura degli acari senza irritazioni della pelle.
-Separazione della polvere e degli acari: il contenitore della polvere presenta un design a doppio contenitore con una capacità totale di 500 ml. Il contenitore sinistro serve per il filtraggio, mentre il contenitore destro raccoglie polvere e acari.
-Tripla filtrazione: questo aspiratore antiacaro include un filtro fine in acciaio inossidabile che trattiene le particelle grossolane, ovatta filtrante ad alta densità che filtra particelle fino a 0,3 micron e un contenitore trasparente per catturare particelle visibili e più grandi.
-Riutilizzabile: il contenitore della polvere è rimovibile, si smonta facilmente con un solo pulsante e può essere riutilizzato dopo la pulizia.</t>
+          <t>Potente aspirazione da 20 kPa e spazzola a rullo in metallo per una pulizia efficace: Il potente motore rimuove efficacemente polvere, sporco, acari della polvere, cellule cutanee e peli di animali domestici da materassi, divani, tappeti, biancheria da letto e peluche. La spazzola a rullo in metallo, grazie alla sua struttura robusta, genera vibrazioni più intense rispetto alle tradizionali spazzole in plastica e contribuisce a una pulizia più profonda dei tessuti.
+Pulizia profonda 3-in-1 con luce UV-C, vibrazioni ultrasoniche e funzione di riscaldamento: La combinazione di tecnologia UV-C, vibrazioni meccaniche e calore favorisce una pulizia igienica di materassi e tessuti. Le particelle, la polvere e gli allergeni rimossi vengono quindi aspirati dalla potente forza di aspirazione. Ideale per letti, divani e altre superfici in tessuto.
+Pulizia delicata e adatta alle persone sensibili, con fino al 99,99% di allergeni in meno*: La pulizia avviene senza l'uso di sostanze chimiche, combinando tecnologia UV-C, vibrazioni e calore. Aiuta a ridurre allergeni, acari della polvere e particelle fini, ideale per persone sensibili, camerette e famiglie con animali domestici.
+Aspirapolvere antiacaro versatile per ampie superfici tessili e peli di animali domestici: A differenza dei tradizionali aspirapolvere, questo aspirapolvere per materassi è progettato appositamente per la pulizia diretta di ampie superfici tessili. Ideale per materassi, divani, tappeti, biancheria da letto e imbottiti, rimuove efficacemente polvere e peli di animali domestici per una casa più pulita e igienica.
+Libertà senza fili per una pulizia flessibile: Il design senza fili consente una pulizia comoda e senza l'ingombro del cavo di alimentazione. L'aspirapolvere antiacaro offre un'autonomia fino a 45 minuti, ideale per pulire diverse superfici tessili. Grazie alla porta Type-C, il dispositivo può essere ricaricato comodamente. Nota: cavo di ricarica Type-C incluso, alimentatore non incluso.
+Gli acari della polvere non sono visibili a occhio nudo: Si trovano spesso nei tessuti e si nutrono, tra l'altro, di cellule cutanee. Per questo possono rimanere inosservati anche dopo la normale pulizia. L'aspirapolvere antiacaro Lubluelu favorisce una cura igienica dei tessuti combinando luce UV-C, calore e vibrazioni per rimuovere le particelle e aspirarle efficacemente. Aiuta a rimuovere fino al 99,99% degli allergeni, per un ambiente domestico più pulito.</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41+tCP4liDL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31VKof2lcLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0HH8ND3PS</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -12768,7 +12681,7 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>1441388</v>
+        <v>141227</v>
       </c>
       <c r="P35" s="15"/>
       <c r="Q35" s="16">
@@ -12781,7 +12694,7 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T35" s="15"/>
@@ -12790,15 +12703,23 @@
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="Z35" s="20">
+        <v>89.99</v>
+      </c>
       <c r="AA35" s="4"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="15"/>
-      <c r="AD35" s="19"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="21"/>
+      <c r="AD35" s="19">
+        <v>83</v>
+      </c>
+      <c r="AE35" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
@@ -12818,8 +12739,14 @@
       <c r="AO35" s="13"/>
       <c r="AP35" s="4"/>
       <c r="AQ35" s="19"/>
-      <c r="AR35" s="19"/>
-      <c r="AS35" s="14"/>
+      <c r="AR35" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12829,7 +12756,11 @@
       <c r="AV35" s="14"/>
       <c r="AW35" s="13"/>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
+      <c r="AY35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -12843,12 +12774,24 @@
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23"/>
-      <c r="BJ35" s="23"/>
-      <c r="BK35" s="23"/>
+      <c r="BI35" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BJ35" s="23" t="inlineStr">
+        <is>
+          <t>1000 Grammi</t>
+        </is>
+      </c>
+      <c r="BK35" s="23" t="inlineStr">
+        <is>
+          <t>1,000.00 g</t>
+        </is>
+      </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>34L x 28l x 22H cm</t>
+          <t>25L x 20l x 15H cm</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
@@ -12857,385 +12800,6 @@
       <c r="BP35" s="23"/>
       <c r="BQ35" s="23"/>
       <c r="BR35" s="13"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>B0H418FY5Y</t>
-        </is>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Lubluelu | Caratteristica speciale: Luce UV | Superfici consigliate: Tappezzeria | Fonte di alimentazione: Con cavo elettrico | È cordless?: No</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Pulitore per materassi 3 in 1 con potenza di aspirazione da 20 kPa, aspirapolvere antiacaro con funzione battitore e funzione di calore, aspirapolvere manuale per materassi, divani e</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>Tecnologia di pulizia 3 in 1 per tessuti igienici: la combinazione di spazzola rotante, funzione battitore e supporto termico aiuta a rimuovere polvere, acari e allergeni dalle superfici del tessuto e a migliorare la pulizia di materassi e mobili imbottiti.
-Potente aspirazione da 20 kPa per una pulizia profonda: con una forte potenza di aspirazione di 20.000 Pa, l'aspirapolvere acari rimuove in modo affidabile polvere, sporco e particelle sottili da materassi, divani, piumini, tappeti e altre superfici tessili.
-Versatile su varie superfici in tessuto: ideale per materassi, tappezzeria, lenzuola, coperte, tappeti e peluche. Perfettamente adatto per la pulizia regolare di camera da letto, soggiorno e cameretta dei bambini.
-Pulizia senza additivi chimici: la combinazione di movimento meccanico e funzione termica supporta una pulizia efficace senza detergenti aggiuntivi. Particolarmente adatto per case con bambini, animali domestici o persone allergiche.
-Design compatto per una comoda maneggevolezza: il leggero dispositivo portatile dispone di un cavo di alimentazione da 4 metri per una maggiore libertà di movimento. Il contenitore della polvere è facile da svuotare e il sistema di filtraggio è facile da pulire per l'uso quotidiano.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H418FY5Y?psc=1</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L36" s="14" t="inlineStr">
-        <is>
-          <t>B0H418FY5Y</t>
-        </is>
-      </c>
-      <c r="M36" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N36" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O36" s="15">
-        <v>228781</v>
-      </c>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="16">
-        <v>0</v>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S36" s="18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="T36" s="15"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="20">
-        <v>99.99</v>
-      </c>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="15"/>
-      <c r="AD36" s="19">
-        <v>18</v>
-      </c>
-      <c r="AE36" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="21">
-        <v>4.3</v>
-      </c>
-      <c r="AG36" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="20"/>
-      <c r="AI36" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ36"/>
-      <c r="AK36" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AL36" s="19">
-        <v>49</v>
-      </c>
-      <c r="AM36" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN36" s="13"/>
-      <c r="AO36" s="13"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="19"/>
-      <c r="AR36" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS36" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Official</t>
-        </is>
-      </c>
-      <c r="AT36" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
-        </is>
-      </c>
-      <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
-      <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
-      <c r="BB36" s="13"/>
-      <c r="BC36" s="13"/>
-      <c r="BD36" s="13"/>
-      <c r="BE36" s="13"/>
-      <c r="BF36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG36" s="13"/>
-      <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
-      <c r="BJ36" s="23" t="inlineStr">
-        <is>
-          <t>2,34 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK36" s="23" t="inlineStr">
-        <is>
-          <t>2.34 kg</t>
-        </is>
-      </c>
-      <c r="BL36" s="23" t="inlineStr">
-        <is>
-          <t>42L x 31l x 18H cm</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36" s="23"/>
-      <c r="BQ36" s="23"/>
-      <c r="BR36" s="13"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>36</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>B0HFN6BP5R</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>Colore: Bianco Crema + Argento</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>Marchio: Lubluelu | Caratteristica speciale: Luce UV | Tipo di filtro: Filtro in acciaio inox e spugna | Superfici consigliate: Materassi, divani, tappeti, biancheria da letto, imbottiti, tessuti | Fonte di alimentazione: A batteria</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0HFN6BP5R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Aspirapolvere Antiacaro 20kPa Senza Fili per Materassi UV-C</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>Potente aspirazione da 20 kPa e spazzola a rullo in metallo per una pulizia efficace: Il potente motore rimuove efficacemente polvere, sporco, acari della polvere, cellule cutanee e peli di animali domestici da materassi, divani, tappeti, biancheria da letto e peluche. La spazzola a rullo in metallo, grazie alla sua struttura robusta, genera vibrazioni più intense rispetto alle tradizionali spazzole in plastica e contribuisce a una pulizia più profonda dei tessuti.
-Pulizia profonda 3-in-1 con luce UV-C, vibrazioni ultrasoniche e funzione di riscaldamento: La combinazione di tecnologia UV-C, vibrazioni meccaniche e calore favorisce una pulizia igienica di materassi e tessuti. Le particelle, la polvere e gli allergeni rimossi vengono quindi aspirati dalla potente forza di aspirazione. Ideale per letti, divani e altre superfici in tessuto.
-Pulizia delicata e adatta alle persone sensibili, con fino al 99,99% di allergeni in meno*: La pulizia avviene senza l'uso di sostanze chimiche, combinando tecnologia UV-C, vibrazioni e calore. Aiuta a ridurre allergeni, acari della polvere e particelle fini, ideale per persone sensibili, camerette e famiglie con animali domestici.
-Aspirapolvere antiacaro versatile per ampie superfici tessili e peli di animali domestici: A differenza dei tradizionali aspirapolvere, questo aspirapolvere per materassi è progettato appositamente per la pulizia diretta di ampie superfici tessili. Ideale per materassi, divani, tappeti, biancheria da letto e imbottiti, rimuove efficacemente polvere e peli di animali domestici per una casa più pulita e igienica.
-Libertà senza fili per una pulizia flessibile: Il design senza fili consente una pulizia comoda e senza l'ingombro del cavo di alimentazione. L'aspirapolvere antiacaro offre un'autonomia fino a 45 minuti, ideale per pulire diverse superfici tessili. Grazie alla porta Type-C, il dispositivo può essere ricaricato comodamente. Nota: cavo di ricarica Type-C incluso, alimentatore non incluso.
-Gli acari della polvere non sono visibili a occhio nudo: Si trovano spesso nei tessuti e si nutrono, tra l'altro, di cellule cutanee. Per questo possono rimanere inosservati anche dopo la normale pulizia. L'aspirapolvere antiacaro Lubluelu favorisce una cura igienica dei tessuti combinando luce UV-C, calore e vibrazioni per rimuovere le particelle e aspirarle efficacemente. Aiuta a rimuovere fino al 99,99% degli allergeni, per un ambiente domestico più pulito.</t>
-        </is>
-      </c>
-      <c r="J37" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0HFN6BP5R?psc=1</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31VKof2lcLL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L37" s="14" t="inlineStr">
-        <is>
-          <t>B0HH8ND3PS</t>
-        </is>
-      </c>
-      <c r="M37" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O37" s="15">
-        <v>141227</v>
-      </c>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="16">
-        <v>0</v>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere per futon</t>
-        </is>
-      </c>
-      <c r="S37" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T37" s="15"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="19">
-        <v>3</v>
-      </c>
-      <c r="Z37" s="20">
-        <v>89.99</v>
-      </c>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="19">
-        <v>83</v>
-      </c>
-      <c r="AE37" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG37" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="20"/>
-      <c r="AI37" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ37"/>
-      <c r="AK37" s="13"/>
-      <c r="AL37" s="19"/>
-      <c r="AM37" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN37" s="13"/>
-      <c r="AO37" s="13"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="19"/>
-      <c r="AR37" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS37" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT37" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="13"/>
-      <c r="AX37" s="13"/>
-      <c r="AY37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ37" s="13"/>
-      <c r="BA37" s="13"/>
-      <c r="BB37" s="13"/>
-      <c r="BC37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD37" s="13"/>
-      <c r="BE37" s="13"/>
-      <c r="BF37" s="13"/>
-      <c r="BG37" s="13"/>
-      <c r="BH37" s="14"/>
-      <c r="BI37" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BJ37" s="23" t="inlineStr">
-        <is>
-          <t>1000 Grammi</t>
-        </is>
-      </c>
-      <c r="BK37" s="23" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BL37" s="23" t="inlineStr">
-        <is>
-          <t>25L x 20l x 15H cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23"/>
-      <c r="BN37" s="23"/>
-      <c r="BO37" s="23"/>
-      <c r="BP37" s="23"/>
-      <c r="BQ37" s="23"/>
-      <c r="BR37" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13388,143 +12952,128 @@
     <hyperlink ref="M20" r:id="rId145" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N20" r:id="rId146"/>
     <hyperlink ref="AW20" r:id="rId147" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
-    <hyperlink ref="C21" r:id="rId148" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
-    <hyperlink ref="G21" r:id="rId149" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=ERINGOGO"/>
-    <hyperlink ref="J21" r:id="rId150" tooltip="https://www.amazon.it/dp/B0F8W81X7Y?psc=1"/>
-    <hyperlink ref="K21" r:id="rId151" tooltip="https://m.media-amazon.com/images/I/41y457dzzRL._AC_US200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId152" tooltip="https://www.amazon.it/dp/B0F8W81X7Y"/>
+    <hyperlink ref="C21" r:id="rId148" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G21" r:id="rId149" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J21" r:id="rId150" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K21" r:id="rId151" tooltip="https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId152" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
     <hyperlink ref="M21" r:id="rId153" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N21" r:id="rId154"/>
-    <hyperlink ref="C22" r:id="rId155" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G22" r:id="rId156" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J22" r:id="rId157" tooltip="https://www.amazon.it/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K22" r:id="rId158" tooltip="https://m.media-amazon.com/images/I/41skTyVFYpL._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId159" tooltip="https://www.amazon.it/dp/B0F9NJM4V9"/>
-    <hyperlink ref="M22" r:id="rId160" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N22" r:id="rId161"/>
-    <hyperlink ref="AW22" r:id="rId162" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C23" r:id="rId163" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
-    <hyperlink ref="G23" r:id="rId164" tooltip="https://www.amazon.it/stores/Elecbee/page/523E80A7-9683-4D7C-910D-BDB5D37DE32D?lp_asin=B0FBRWMG4G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J23" r:id="rId165" tooltip="https://www.amazon.it/dp/B0FBRWMG4G?psc=1"/>
-    <hyperlink ref="K23" r:id="rId166" tooltip="https://m.media-amazon.com/images/I/41Ol8d1f4bL._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId167" tooltip="https://www.amazon.it/dp/B0H465J5XB"/>
-    <hyperlink ref="M23" r:id="rId168" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N23" r:id="rId169"/>
-    <hyperlink ref="AW23" r:id="rId170" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
-    <hyperlink ref="C24" r:id="rId171" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="G24" r:id="rId172" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId173" tooltip="https://www.amazon.it/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K24" r:id="rId174" tooltip="https://m.media-amazon.com/images/I/31va0mFb48L._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId175" tooltip="https://www.amazon.it/dp/B0FDWVV95V"/>
-    <hyperlink ref="M24" r:id="rId176" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N24" r:id="rId177"/>
-    <hyperlink ref="AW24" r:id="rId178" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD"/>
-    <hyperlink ref="C25" r:id="rId179" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="G25" r:id="rId180" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J25" r:id="rId181" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
-    <hyperlink ref="K25" r:id="rId182" tooltip="https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId183" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
-    <hyperlink ref="M25" r:id="rId184" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N25" r:id="rId185"/>
-    <hyperlink ref="AW25" r:id="rId186" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C26" r:id="rId187" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="G26" r:id="rId188" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J26" r:id="rId189" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
-    <hyperlink ref="K26" r:id="rId190" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId191" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
-    <hyperlink ref="M26" r:id="rId192" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N26" r:id="rId193"/>
-    <hyperlink ref="AW26" r:id="rId194" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C27" r:id="rId195" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
-    <hyperlink ref="G27" r:id="rId196" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
-    <hyperlink ref="J27" r:id="rId197" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
-    <hyperlink ref="K27" r:id="rId198" tooltip="https://m.media-amazon.com/images/I/41B+I610d+L._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId199" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="AW21" r:id="rId155" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C22" r:id="rId156" tooltip="https://www.amazon.it/dp/B0FBRWMG4G"/>
+    <hyperlink ref="G22" r:id="rId157" tooltip="https://www.amazon.it/stores/Elecbee/page/523E80A7-9683-4D7C-910D-BDB5D37DE32D?lp_asin=B0FBRWMG4G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J22" r:id="rId158" tooltip="https://www.amazon.it/dp/B0FBRWMG4G?psc=1"/>
+    <hyperlink ref="K22" r:id="rId159" tooltip="https://m.media-amazon.com/images/I/41Ol8d1f4bL._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId160" tooltip="https://www.amazon.it/dp/B0H465J5XB"/>
+    <hyperlink ref="M22" r:id="rId161" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N22" r:id="rId162"/>
+    <hyperlink ref="AW22" r:id="rId163" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WTTH4P2M430O"/>
+    <hyperlink ref="C23" r:id="rId164" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="G23" r:id="rId165" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J23" r:id="rId166" tooltip="https://www.amazon.it/dp/B0FKRC3KQY?psc=1"/>
+    <hyperlink ref="K23" r:id="rId167" tooltip="https://m.media-amazon.com/images/I/31SPlR-BXSL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId168" tooltip="https://www.amazon.it/dp/B0FKRC3KQY"/>
+    <hyperlink ref="M23" r:id="rId169" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N23" r:id="rId170"/>
+    <hyperlink ref="AW23" r:id="rId171" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C24" r:id="rId172" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="G24" r:id="rId173" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J24" r:id="rId174" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ?psc=1"/>
+    <hyperlink ref="K24" r:id="rId175" tooltip="https://images-na.ssl-images-amazon.com/images/I/511XZVAimmL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId176" tooltip="https://www.amazon.it/dp/B0FMRNV3RZ"/>
+    <hyperlink ref="M24" r:id="rId177" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N24" r:id="rId178"/>
+    <hyperlink ref="AW24" r:id="rId179" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C25" r:id="rId180" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="G25" r:id="rId181" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Teant"/>
+    <hyperlink ref="J25" r:id="rId182" tooltip="https://www.amazon.it/dp/B0FN3GPQZM?psc=1"/>
+    <hyperlink ref="K25" r:id="rId183" tooltip="https://m.media-amazon.com/images/I/41B+I610d+L._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId184" tooltip="https://www.amazon.it/dp/B0FN3GPQZM"/>
+    <hyperlink ref="M25" r:id="rId185" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N25" r:id="rId186"/>
+    <hyperlink ref="AW25" r:id="rId187" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
+    <hyperlink ref="C26" r:id="rId188" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="G26" r:id="rId189" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi"/>
+    <hyperlink ref="J26" r:id="rId190" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
+    <hyperlink ref="K26" r:id="rId191" tooltip="https://m.media-amazon.com/images/I/215WpAtX06L._AC_US200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId192" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="M26" r:id="rId193" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N26" r:id="rId194"/>
+    <hyperlink ref="C27" r:id="rId195" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
+    <hyperlink ref="G27" r:id="rId196" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J27" r:id="rId197" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
+    <hyperlink ref="K27" r:id="rId198" tooltip="https://m.media-amazon.com/images/I/41FJHPfdNGL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId199" tooltip="https://www.amazon.it/dp/B0C5372Y5G"/>
     <hyperlink ref="M27" r:id="rId200" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N27" r:id="rId201"/>
-    <hyperlink ref="AW27" r:id="rId202" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EVTWEH1TBVG5"/>
-    <hyperlink ref="C28" r:id="rId203" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
-    <hyperlink ref="G28" r:id="rId204" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=PattenlLevi"/>
-    <hyperlink ref="J28" r:id="rId205" tooltip="https://www.amazon.it/dp/B0FP52HNHM?psc=1"/>
-    <hyperlink ref="K28" r:id="rId206" tooltip="https://m.media-amazon.com/images/I/215WpAtX06L._AC_US200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId207" tooltip="https://www.amazon.it/dp/B0FP52HNHM"/>
+    <hyperlink ref="AW27" r:id="rId202" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C28" r:id="rId203" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="G28" r:id="rId204" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD"/>
+    <hyperlink ref="J28" r:id="rId205" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
+    <hyperlink ref="K28" r:id="rId206" tooltip="https://m.media-amazon.com/images/I/51Q5Ecf20kL._AC_US200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId207" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
     <hyperlink ref="M28" r:id="rId208" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N28" r:id="rId209"/>
-    <hyperlink ref="C29" r:id="rId210" tooltip="https://www.amazon.it/dp/B0FP9CGZYN"/>
-    <hyperlink ref="G29" r:id="rId211" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J29" r:id="rId212" tooltip="https://www.amazon.it/dp/B0FP9CGZYN?psc=1"/>
-    <hyperlink ref="K29" r:id="rId213" tooltip="https://m.media-amazon.com/images/I/41FJHPfdNGL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId214" tooltip="https://www.amazon.it/dp/B0C5372Y5G"/>
+    <hyperlink ref="C29" r:id="rId210" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="G29" r:id="rId211" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId212" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
+    <hyperlink ref="K29" r:id="rId213" tooltip="https://m.media-amazon.com/images/I/41TzkiwaXvL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId214" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
     <hyperlink ref="M29" r:id="rId215" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N29" r:id="rId216"/>
-    <hyperlink ref="AW29" r:id="rId217" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C30" r:id="rId218" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
-    <hyperlink ref="G30" r:id="rId219" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MITE+GUARD"/>
-    <hyperlink ref="J30" r:id="rId220" tooltip="https://www.amazon.it/dp/B0FRBB876G?psc=1"/>
-    <hyperlink ref="K30" r:id="rId221" tooltip="https://m.media-amazon.com/images/I/51Q5Ecf20kL._AC_US200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId222" tooltip="https://www.amazon.it/dp/B0FRBB876G"/>
+    <hyperlink ref="AW29" r:id="rId217" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
+    <hyperlink ref="C30" r:id="rId218" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
+    <hyperlink ref="G30" r:id="rId219" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J30" r:id="rId220" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K30" r:id="rId221" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId222" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
     <hyperlink ref="M30" r:id="rId223" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N30" r:id="rId224"/>
-    <hyperlink ref="C31" r:id="rId225" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
-    <hyperlink ref="G31" r:id="rId226" tooltip="https://www.amazon.it/stores/JIGOO-IT/page/7F1C5254-18CC-4331-A449-F5F68B2E288D?lp_asin=B0FW3MWVJR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId227" tooltip="https://www.amazon.it/dp/B0FW3MWVJR?psc=1"/>
-    <hyperlink ref="K31" r:id="rId228" tooltip="https://m.media-amazon.com/images/I/41TzkiwaXvL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId229" tooltip="https://www.amazon.it/dp/B0FW3MWVJR"/>
+    <hyperlink ref="C31" r:id="rId225" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
+    <hyperlink ref="G31" r:id="rId226" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J31" r:id="rId227" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
+    <hyperlink ref="K31" r:id="rId228" tooltip="https://m.media-amazon.com/images/I/31vsJlUl+mL._AC_US200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId229" tooltip="https://www.amazon.it/dp/B0HG52FLCZ"/>
     <hyperlink ref="M31" r:id="rId230" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N31" r:id="rId231"/>
-    <hyperlink ref="AW31" r:id="rId232" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A99P1VJD8HKQ6"/>
-    <hyperlink ref="C32" r:id="rId233" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="G32" r:id="rId234" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J32" r:id="rId235" tooltip="https://www.amazon.it/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K32" r:id="rId236" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId237" tooltip="https://www.amazon.it/dp/B0FYM1D13D"/>
-    <hyperlink ref="M32" r:id="rId238" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N32" r:id="rId239"/>
-    <hyperlink ref="C33" r:id="rId240" tooltip="https://www.amazon.it/dp/B0GJS592V3"/>
-    <hyperlink ref="G33" r:id="rId241" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J33" r:id="rId242" tooltip="https://www.amazon.it/dp/B0GJS592V3?psc=1"/>
-    <hyperlink ref="K33" r:id="rId243" tooltip="https://m.media-amazon.com/images/I/31vsJlUl+mL._AC_US200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId244" tooltip="https://www.amazon.it/dp/B0HG52FLCZ"/>
+    <hyperlink ref="C32" r:id="rId232" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
+    <hyperlink ref="G32" r:id="rId233" tooltip="https://www.amazon.it/XINYUDAILY/b/ref=bl_dp_s_web_85008070031?ie=UTF8&amp;node=85008070031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
+    <hyperlink ref="J32" r:id="rId234" tooltip="https://www.amazon.it/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K32" r:id="rId235" tooltip="https://m.media-amazon.com/images/I/51XxVKRglXL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId236" tooltip="https://www.amazon.it/dp/B0GXBZHWFJ"/>
+    <hyperlink ref="M32" r:id="rId237" tooltip="https://www.amazon.it/b?node=13713022031"/>
+    <hyperlink ref="N32" r:id="rId238"/>
+    <hyperlink ref="AW32" r:id="rId239" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
+    <hyperlink ref="C33" r:id="rId240" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="G33" r:id="rId241" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
+    <hyperlink ref="J33" r:id="rId242" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K33" r:id="rId243" tooltip="https://m.media-amazon.com/images/I/41+tCP4liDL._AC_US200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId244" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
     <hyperlink ref="M33" r:id="rId245" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N33" r:id="rId246"/>
-    <hyperlink ref="C34" r:id="rId247" tooltip="https://www.amazon.it/dp/B0GT17NK5X"/>
-    <hyperlink ref="G34" r:id="rId248" tooltip="https://www.amazon.it/XINYUDAILY/b/ref=bl_dp_s_web_85008070031?ie=UTF8&amp;node=85008070031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
-    <hyperlink ref="J34" r:id="rId249" tooltip="https://www.amazon.it/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K34" r:id="rId250" tooltip="https://m.media-amazon.com/images/I/51XxVKRglXL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId251" tooltip="https://www.amazon.it/dp/B0GXBZHWFJ"/>
+    <hyperlink ref="C34" r:id="rId247" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
+    <hyperlink ref="G34" r:id="rId248" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId249" tooltip="https://www.amazon.it/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="K34" r:id="rId250" tooltip="https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId251" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
     <hyperlink ref="M34" r:id="rId252" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N34" r:id="rId253"/>
-    <hyperlink ref="AW34" r:id="rId254" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
-    <hyperlink ref="C35" r:id="rId255" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
-    <hyperlink ref="G35" r:id="rId256" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vehiwell"/>
-    <hyperlink ref="J35" r:id="rId257" tooltip="https://www.amazon.it/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K35" r:id="rId258" tooltip="https://m.media-amazon.com/images/I/41+tCP4liDL._AC_US200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId259" tooltip="https://www.amazon.it/dp/B0GTYZLWW3"/>
+    <hyperlink ref="AW34" r:id="rId254" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
+    <hyperlink ref="C35" r:id="rId255" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
+    <hyperlink ref="G35" r:id="rId256" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0HFN6BP5R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J35" r:id="rId257" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
+    <hyperlink ref="K35" r:id="rId258" tooltip="https://m.media-amazon.com/images/I/31VKof2lcLL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId259" tooltip="https://www.amazon.it/dp/B0HH8ND3PS"/>
     <hyperlink ref="M35" r:id="rId260" tooltip="https://www.amazon.it/b?node=13713022031"/>
     <hyperlink ref="N35" r:id="rId261"/>
-    <hyperlink ref="C36" r:id="rId262" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
-    <hyperlink ref="G36" r:id="rId263" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0H418FY5Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J36" r:id="rId264" tooltip="https://www.amazon.it/dp/B0H418FY5Y?psc=1"/>
-    <hyperlink ref="K36" r:id="rId265" tooltip="https://m.media-amazon.com/images/I/41WpJwb0PhL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId266" tooltip="https://www.amazon.it/dp/B0H418FY5Y"/>
-    <hyperlink ref="M36" r:id="rId267" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N36" r:id="rId268"/>
-    <hyperlink ref="AW36" r:id="rId269" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
-    <hyperlink ref="C37" r:id="rId270" tooltip="https://www.amazon.it/dp/B0HFN6BP5R"/>
-    <hyperlink ref="G37" r:id="rId271" tooltip="https://www.amazon.it/stores/Lubluelu/page/14418463-A3CB-412E-B0D5-36E2BEE36429?lp_asin=B0HFN6BP5R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId272" tooltip="https://www.amazon.it/dp/B0HFN6BP5R?psc=1"/>
-    <hyperlink ref="K37" r:id="rId273" tooltip="https://m.media-amazon.com/images/I/31VKof2lcLL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId274" tooltip="https://www.amazon.it/dp/B0HH8ND3PS"/>
-    <hyperlink ref="M37" r:id="rId275" tooltip="https://www.amazon.it/b?node=13713022031"/>
-    <hyperlink ref="N37" r:id="rId276"/>
   </hyperlinks>
-  <drawing r:id="rId277"/>
+  <drawing r:id="rId262"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -13739,7 +13288,7 @@
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>ERINGOGO</t>
+          <t>Elecbee</t>
         </is>
       </c>
       <c r="B10" s="15">
@@ -13758,7 +13307,7 @@
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Elecbee</t>
+          <t>FEPPO</t>
         </is>
       </c>
       <c r="B11" s="15">
@@ -13777,7 +13326,7 @@
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>FEPPO</t>
+          <t>Fey</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -13796,7 +13345,7 @@
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Fey</t>
+          <t>Lambluefly</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -13815,7 +13364,7 @@
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Lambluefly</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -13834,7 +13383,7 @@
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>Lubluelu</t>
         </is>
       </c>
       <c r="B15" s="15">
@@ -13853,7 +13402,7 @@
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>MITE GUARD</t>
         </is>
       </c>
       <c r="B16" s="15">
@@ -13872,7 +13421,7 @@
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>MITE GUARD</t>
+          <t>Mayking</t>
         </is>
       </c>
       <c r="B17" s="15">
@@ -13891,7 +13440,7 @@
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Mayking</t>
+          <t>PattenlLevi</t>
         </is>
       </c>
       <c r="B18" s="15">
@@ -13910,7 +13459,7 @@
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>PattenlLevi</t>
+          <t>SIKITUT</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -13929,7 +13478,7 @@
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>SIKITUT</t>
+          <t>Teant</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -13948,7 +13497,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Teant</t>
+          <t>Tiazhan</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -13967,7 +13516,7 @@
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan</t>
+          <t>Vehiwell</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -13986,7 +13535,7 @@
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell</t>
+          <t>Vihoom</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -14005,7 +13554,7 @@
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Vihoom</t>
+          <t>XINYUDAILY</t>
         </is>
       </c>
       <c r="B24" s="15">
@@ -14024,7 +13573,7 @@
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>XINYUDAILY</t>
+          <t>Yaasier</t>
         </is>
       </c>
       <c r="B25" s="15">
@@ -14037,25 +13586,6 @@
       <c r="E25" s="15"/>
       <c r="F25" s="20"/>
       <c r="G25" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Yaasier</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <v>0</v>
-      </c>
-      <c r="C26" s="15">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -14067,7 +13597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -14523,25 +14053,6 @@
       <c r="E22" s="15"/>
       <c r="F22" s="20"/>
       <c r="G22" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>yefengdianzi</t>
-        </is>
-      </c>
-      <c r="B23" s="15">
-        <v>0</v>
-      </c>
-      <c r="C23" s="15">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="22">
         <v>0.0</v>
       </c>
     </row>
